--- a/incomplete/reu/koschnich.xlsx
+++ b/incomplete/reu/koschnich.xlsx
@@ -1,615 +1,582 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venit\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54DCA385-B12C-4CE6-9A56-60AAC6CCEEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" xr2:uid="{0221817C-97EB-4300-8D7A-BEFF8A2B6B96}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R92f784945d7f4bbb"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="124">
-  <si>
-    <t>REACTION</t>
-  </si>
-  <si>
-    <t>VARIANTS</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>Reaction Type</t>
-  </si>
-  <si>
-    <t>EXPERIMENTER</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>DOI</t>
-  </si>
-  <si>
-    <t>Publication URL</t>
-  </si>
-  <si>
-    <t>Record Created</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>REACTANT</t>
-  </si>
-  <si>
-    <t>SMILES</t>
-  </si>
-  <si>
-    <t>Amount (millimole)</t>
-  </si>
-  <si>
-    <t>PRODUCT</t>
-  </si>
-  <si>
-    <t>Yield (%)</t>
-  </si>
-  <si>
-    <t>Erik Koshnicharski</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Ball Mill</t>
-  </si>
-  <si>
-    <t>Duration (Min)</t>
-  </si>
-  <si>
-    <t>Frequency (Hz)</t>
-  </si>
-  <si>
-    <t>ball_material</t>
-  </si>
-  <si>
-    <t>number_of_balls</t>
-  </si>
-  <si>
-    <t>ball_radius (mm)</t>
-  </si>
-  <si>
-    <t>MECHANOCHEMISTRY</t>
-  </si>
-  <si>
-    <t>ADDITIVE</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>amount (mmol)</t>
-  </si>
-  <si>
-    <t>Sodium Methoxide</t>
-  </si>
-  <si>
-    <t>DMSO</t>
-  </si>
-  <si>
-    <t>NIS</t>
-  </si>
-  <si>
-    <t>amount (µL)</t>
-  </si>
-  <si>
-    <t>MeCN</t>
-  </si>
-  <si>
-    <t>Stainless Steel</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccccc2</t>
-  </si>
-  <si>
-    <t>Cc2ccc(C=c1c(C)noc1=O)cc2</t>
-  </si>
-  <si>
-    <t>COc2ccc(C=c1c(C)noc1=O)cc2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccc(Cl)cc2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccc(Br)cc2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccc(C(F)(F)F)cc2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccc(N(=O)=O)cc2</t>
-  </si>
-  <si>
-    <t>Cc2cccc(C=c1c(C)noc1=O)c2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2cccc(Cl)c2</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2cccc(Br)c2</t>
-  </si>
-  <si>
-    <t>Cc1ccccc1C=c2c(C)noc2=O</t>
-  </si>
-  <si>
-    <t>Cc2ccc(C=c1c(C)noc1=O)cc2C</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccc(Cl)c(Cl)c2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Addition / (Spiro) Cyclization </t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc3ccc2ccccc2c3</t>
-  </si>
-  <si>
-    <t>Cc1noc(=O)c1=Cc2ccco2</t>
-  </si>
-  <si>
-    <t>CCc1noc(=O)c1=Cc2ccccc2</t>
-  </si>
-  <si>
-    <t>erikkoshnicharski@gmail.com</t>
-  </si>
-  <si>
-    <t>C1(=O)/C(=C/C2C=CC=CC=2)/C(C2C=CC=CC=2)=NO1</t>
-  </si>
-  <si>
-    <t>C1(=O)/C(=C/C2C=CC=CC=2)/C(C)=NO1</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCCCCCC)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC(OC)=CC=1)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC(Cl)=CC=1)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=C(F)C=1)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1Cl)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCCC1C=CC=CC=1)=C/C(OCC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1)=C/C(OC)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1)=C/C(OC(C)C)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1)=C/C(OCC(C)C)=O</t>
-  </si>
-  <si>
-    <t>C/C(/NCC1C=CC=CC=1)=C/C(OC(C)(C)C)=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(C)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(C)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(OC)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(OC)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(Cl)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(Cl)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(Br)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(Br)=CC=2)[C@@]21C(C)=NOC2=O</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(C(F)(F)F)=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC([N+]([O-])=O)=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Cl)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Br)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=CC=1C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(C)=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(Cl)=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=C2C=CC=CC2=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1OC=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2CC</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C1C=CC=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCCCCCC)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC(OC)=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC(Cl)=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=C(F)C=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2Cl)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OC(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OC(C)(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(C(F)(F)F)=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC([N+]([O-])=O)=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Cl)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Br)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=CC=1C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(C)=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(Cl)=C(C)C=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=C2C=CC=CC2=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1OC=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2CC</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C1C=CC=CC=1</t>
-  </si>
-  <si>
-    <t>C1C(NCCCCCC)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC(OC)=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC(Cl)=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=C(F)C=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2Cl)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(=O)OC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OC(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OCC(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>C1C(NCC2C=CC=CC=2)=C(C(OC(C)(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</t>
-  </si>
-  <si>
-    <t>10.1039/d4mr00125g</t>
-  </si>
-  <si>
-    <t>https://pubs.rsc.org/mr/article/2/2/317/855829/Chemodivergent-and-diastereoselective-synthesis-of</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>School of Chemical and Environmental Engineering, Anhui Polytechnic University</t>
-  </si>
-  <si>
-    <t>Wuhu</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t xml:space="preserve">REACTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reaction Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EXPERIMENTER</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">City</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DOI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Publication URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Record Created</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Email</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Michael Addition / (Spiro) Cyclization </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">School of Chemical and Environmental Engineering, Anhui Polytechnic University</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wuhu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10.1039/d4mr00125g</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://pubs.rsc.org/mr/article/2/2/317/855829/Chemodivergent-and-diastereoselective-synthesis-of</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Erik Koshnicharski</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">erikkoshnicharski@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VARIANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">REACTANT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PRODUCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ADDITIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MECHANOCHEMISTRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SMILES</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Amount (millimole)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yield (%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">amount (mmol)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Frequency (Hz)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ball_material</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">number_of_balls</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccccc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMSO</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ball Mill</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Stainless Steel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc2ccc(C=c1c(C)noc1=O)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(C)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">COc2ccc(C=c1c(C)noc1=O)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(OC)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccc(Cl)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(Cl)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccc(Br)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC(Br)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccc(C(F)(F)F)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(C(F)(F)F)=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccc(N(=O)=O)cc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc2cccc(C=c1c(C)noc1=O)c2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@H]([C@]21C(=O)ON=C2C)C1C=CC([N+]([O-])=O)=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2cccc(Cl)c2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Cl)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2cccc(Br)c2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Br)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1ccccc1C=c2c(C)noc2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC=CC=1C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc2ccc(C=c1c(C)noc1=O)cc2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(C)=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccc(Cl)c(Cl)c2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=CC(Cl)=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc3ccc2ccccc2c3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1C=C2C=CC=CC2=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cc1noc(=O)c1=Cc2ccco2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H]([C@]21C(=O)ON=C2C)C1OC=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CCc1noc(=O)c1=Cc2ccccc2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2CC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1(=O)/C(=C/C2C=CC=CC=2)/C(C2C=CC=CC=2)=NO1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C1C=CC=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1(=O)/C(=C/C2C=CC=CC=2)/C(C)=NO1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCCCCCC)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCCCCCC)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC(OC)=CC=1)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC(OC)=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC(Cl)=CC=1)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC(Cl)=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=C(F)C=1)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=C(F)C=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1Cl)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2Cl)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCCC1C=CC=CC=1)=C/C(OCC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1)=C/C(OC)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OC)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1)=C/C(OC(C)C)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OC(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1)=C/C(OCC(C)C)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C/C(/NCC1C=CC=CC=1)=C/C(OC(C)(C)C)=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OC(C)(C)C)=O)[C@@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MeCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sodium Methoxide</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(C)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(OC)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(Cl)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC(Br)=CC=2)[C@@]21C(C)=NOC2=O</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(C(F)(F)F)=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC)=O)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC([N+]([O-])=O)=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Cl)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=C(Br)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC=CC=1C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(C)=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=CC(Cl)=C(C)C=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1C=C2C=CC=CC2=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@@H]([C@]21C(=O)ON=C2C)C1OC=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2CC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C1C=CC=CC=1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCCCCCC)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC(OC)=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC(Cl)=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=C(F)C=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2Cl)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCCC2C=CC=CC=2)=C(C(=O)OCC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(=O)OC)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OC(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OCC(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1C(NCC2C=CC=CC=2)=C(C(OC(C)(C)C)=O)[C@H](C2C=CC=CC=2)[C@]21C(=O)ON=C2C</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-  </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-  </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="General"/>
+    <x:numFmt numFmtId="201" formatCode="0%"/>
+    <x:numFmt numFmtId="202" formatCode="0&quot;%&quot;"/>
+  </x:numFmts>
+  <x:fonts count="3">
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF467886"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8E8E8"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="10">
+    <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="43">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -649,162 +616,68 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -812,26 +685,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -843,7 +713,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -861,22 +731,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -891,264 +761,891 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9899164-BB2A-4D91-9A98-DD342DCD0223}">
-  <dimension ref="A1:V63"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.08984375" customWidth="1"/>
-    <col min="13" max="13" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="15.08984375" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.6328125" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="12.26953125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A1" s="2"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
-      <c r="G1" s="9"/>
-      <c r="V1" s="7"/>
+    <row r="1">
+      <c r="A1" s="4"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="11"/>
+      <c r="F1"/>
+      <c r="G1" s="14"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1" s="8"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
+      <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
+      <c r="AI1"/>
+      <c r="AJ1"/>
+      <c r="AK1"/>
+      <c r="AL1"/>
+      <c r="AM1"/>
+      <c r="AN1"/>
+      <c r="AO1"/>
+      <c r="AP1"/>
+      <c r="AQ1"/>
+      <c r="AR1"/>
+      <c r="AS1"/>
+      <c r="AT1"/>
+      <c r="AU1"/>
+      <c r="AV1"/>
+      <c r="AW1"/>
+      <c r="AX1"/>
+      <c r="AY1"/>
+      <c r="AZ1"/>
+      <c r="BA1"/>
+      <c r="BB1"/>
+      <c r="BC1"/>
+      <c r="BD1"/>
+      <c r="BE1"/>
+      <c r="BF1"/>
+      <c r="BG1"/>
+      <c r="BH1"/>
+      <c r="BI1"/>
+      <c r="BJ1"/>
+      <c r="BK1"/>
+      <c r="BL1"/>
+      <c r="BM1"/>
+      <c r="BN1"/>
+      <c r="BO1"/>
+      <c r="BP1"/>
+      <c r="BQ1"/>
+      <c r="BR1"/>
+      <c r="BS1"/>
+      <c r="BT1"/>
+      <c r="BU1"/>
+      <c r="BV1"/>
+      <c r="BW1"/>
+      <c r="BX1"/>
+      <c r="BY1"/>
+      <c r="BZ1"/>
+      <c r="CA1"/>
+      <c r="CB1"/>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
+    <row r="3">
+      <c r="A3" s="4"/>
       <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+      <c r="BE3"/>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
+      <c r="BI3"/>
+      <c r="BJ3"/>
+      <c r="BK3"/>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3"/>
+      <c r="BT3"/>
+      <c r="BU3"/>
+      <c r="BV3"/>
+      <c r="BW3"/>
+      <c r="BX3"/>
+      <c r="BY3"/>
+      <c r="BZ3"/>
+      <c r="CA3"/>
+      <c r="CB3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4" t="s">
         <v>8</v>
       </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+      <c r="BE4"/>
+      <c r="BF4"/>
+      <c r="BG4"/>
+      <c r="BH4"/>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4"/>
+      <c r="BL4"/>
+      <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4"/>
+      <c r="BT4"/>
+      <c r="BU4"/>
+      <c r="BV4"/>
+      <c r="BW4"/>
+      <c r="BX4"/>
+      <c r="BY4"/>
+      <c r="BZ4"/>
+      <c r="CA4"/>
+      <c r="CB4"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="D4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" t="s">
+    <row r="5">
+      <c r="A5" s="4"/>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
+      <c r="C5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+      <c r="BA5"/>
+      <c r="BB5"/>
+      <c r="BC5"/>
+      <c r="BD5"/>
+      <c r="BE5"/>
+      <c r="BF5"/>
+      <c r="BG5"/>
+      <c r="BH5"/>
+      <c r="BI5"/>
+      <c r="BJ5"/>
+      <c r="BK5"/>
+      <c r="BL5"/>
+      <c r="BM5"/>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
+      <c r="BQ5"/>
+      <c r="BR5"/>
+      <c r="BS5"/>
+      <c r="BT5"/>
+      <c r="BU5"/>
+      <c r="BV5"/>
+      <c r="BW5"/>
+      <c r="BX5"/>
+      <c r="BY5"/>
+      <c r="BZ5"/>
+      <c r="CA5"/>
+      <c r="CB5"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>51</v>
-      </c>
+    <row r="6">
+      <c r="A6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6"/>
+      <c r="BB6"/>
+      <c r="BC6"/>
+      <c r="BD6"/>
+      <c r="BE6"/>
+      <c r="BF6"/>
+      <c r="BG6"/>
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
+      <c r="BK6"/>
+      <c r="BL6"/>
+      <c r="BM6"/>
+      <c r="BN6"/>
+      <c r="BO6"/>
+      <c r="BP6"/>
+      <c r="BQ6"/>
+      <c r="BR6"/>
+      <c r="BS6"/>
+      <c r="BT6"/>
+      <c r="BU6"/>
+      <c r="BV6"/>
+      <c r="BW6"/>
+      <c r="BX6"/>
+      <c r="BY6"/>
+      <c r="BZ6"/>
+      <c r="CA6"/>
+      <c r="CB6"/>
     </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
+    <row r="7">
+      <c r="A7" s="4"/>
+      <c r="B7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="28"/>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="28"/>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7"/>
+      <c r="N7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+      <c r="BE7"/>
+      <c r="BF7"/>
+      <c r="BG7"/>
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
+      <c r="BK7"/>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
+      <c r="BP7"/>
+      <c r="BQ7"/>
+      <c r="BR7"/>
+      <c r="BS7"/>
+      <c r="BT7"/>
+      <c r="BU7"/>
+      <c r="BV7"/>
+      <c r="BW7"/>
+      <c r="BX7"/>
+      <c r="BY7"/>
+      <c r="BZ7"/>
+      <c r="CA7"/>
+      <c r="CB7"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" t="s">
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="K8" t="str">
+        <v>Amount (uL)</v>
+      </c>
+      <c r="L8" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Duration (min)</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Ball Radius (millimeter)</v>
+      </c>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8"/>
+      <c r="BB8"/>
+      <c r="BC8"/>
+      <c r="BD8"/>
+      <c r="BE8"/>
+      <c r="BF8"/>
+      <c r="BG8"/>
+      <c r="BH8"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
+      <c r="BK8"/>
+      <c r="BL8"/>
+      <c r="BM8"/>
+      <c r="BN8"/>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8"/>
+      <c r="BR8"/>
+      <c r="BS8"/>
+      <c r="BT8"/>
+      <c r="BU8"/>
+      <c r="BV8"/>
+      <c r="BW8"/>
+      <c r="BX8"/>
+      <c r="BY8"/>
+      <c r="BZ8"/>
+      <c r="CA8"/>
+      <c r="CB8"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
+    <row r="9">
+      <c r="A9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" t="s">
-        <v>20</v>
-      </c>
-      <c r="P8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" t="s">
-        <v>22</v>
-      </c>
-      <c r="S8" t="s">
-        <v>23</v>
-      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="37"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9" s="34"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9" s="34"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9" s="34"/>
+      <c r="U9"/>
+      <c r="V9" s="37"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9"/>
+      <c r="BB9"/>
+      <c r="BC9"/>
+      <c r="BD9"/>
+      <c r="BE9"/>
+      <c r="BF9"/>
+      <c r="BG9"/>
+      <c r="BH9"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9"/>
+      <c r="BL9"/>
+      <c r="BM9"/>
+      <c r="BN9"/>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9"/>
+      <c r="BR9"/>
+      <c r="BS9"/>
+      <c r="BT9"/>
+      <c r="BU9"/>
+      <c r="BV9"/>
+      <c r="BW9"/>
+      <c r="BX9"/>
+      <c r="BY9"/>
+      <c r="BZ9"/>
+      <c r="CA9"/>
+      <c r="CB9"/>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="V9" s="4"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
+    <row r="10">
+      <c r="A10" s="4"/>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>0.2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>0.24</v>
+      </c>
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="C10">
-        <v>0.2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10">
-        <v>0.24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.91</v>
+      <c r="G10" s="42" t="n">
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I10">
         <v>0.24</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K10">
         <v>30</v>
       </c>
+      <c r="L10"/>
+      <c r="M10"/>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O10">
         <v>30</v>
@@ -1157,7 +1654,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R10">
         <v>4</v>
@@ -1165,41 +1662,104 @@
       <c r="S10">
         <v>3</v>
       </c>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10"/>
+      <c r="BB10"/>
+      <c r="BC10"/>
+      <c r="BD10"/>
+      <c r="BE10"/>
+      <c r="BF10"/>
+      <c r="BG10"/>
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
+      <c r="BK10"/>
+      <c r="BL10"/>
+      <c r="BM10"/>
+      <c r="BN10"/>
+      <c r="BO10"/>
+      <c r="BP10"/>
+      <c r="BQ10"/>
+      <c r="BR10"/>
+      <c r="BS10"/>
+      <c r="BT10"/>
+      <c r="BU10"/>
+      <c r="BV10"/>
+      <c r="BW10"/>
+      <c r="BX10"/>
+      <c r="BY10"/>
+      <c r="BZ10"/>
+      <c r="CA10"/>
+      <c r="CB10"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="11" t="s">
+    <row r="11">
+      <c r="A11" s="4"/>
+      <c r="B11" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>0.2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>0.24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="C11">
-        <v>0.2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11">
-        <v>0.24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0.89</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
       <c r="I11">
         <v>0.24</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K11">
         <v>30</v>
       </c>
+      <c r="L11"/>
+      <c r="M11"/>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O11">
         <v>30</v>
@@ -1208,7 +1768,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R11">
         <v>4</v>
@@ -1216,41 +1776,104 @@
       <c r="S11">
         <v>3</v>
       </c>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11"/>
+      <c r="BB11"/>
+      <c r="BC11"/>
+      <c r="BD11"/>
+      <c r="BE11"/>
+      <c r="BF11"/>
+      <c r="BG11"/>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11"/>
+      <c r="BL11"/>
+      <c r="BM11"/>
+      <c r="BN11"/>
+      <c r="BO11"/>
+      <c r="BP11"/>
+      <c r="BQ11"/>
+      <c r="BR11"/>
+      <c r="BS11"/>
+      <c r="BT11"/>
+      <c r="BU11"/>
+      <c r="BV11"/>
+      <c r="BW11"/>
+      <c r="BX11"/>
+      <c r="BY11"/>
+      <c r="BZ11"/>
+      <c r="CA11"/>
+      <c r="CB11"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="11" t="s">
+    <row r="12">
+      <c r="A12" s="4"/>
+      <c r="B12" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>0.2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>0.24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>0.24</v>
+      </c>
+      <c r="J12" t="s">
         <v>36</v>
       </c>
-      <c r="C12">
-        <v>0.2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12">
-        <v>0.24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.85</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12">
-        <v>0.24</v>
-      </c>
-      <c r="J12" t="s">
-        <v>29</v>
-      </c>
       <c r="K12">
         <v>30</v>
       </c>
+      <c r="L12"/>
+      <c r="M12"/>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O12">
         <v>30</v>
@@ -1259,7 +1882,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R12">
         <v>4</v>
@@ -1267,42 +1890,105 @@
       <c r="S12">
         <v>3</v>
       </c>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
+      <c r="AI12"/>
+      <c r="AJ12"/>
+      <c r="AK12"/>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12"/>
+      <c r="BB12"/>
+      <c r="BC12"/>
+      <c r="BD12"/>
+      <c r="BE12"/>
+      <c r="BF12"/>
+      <c r="BG12"/>
+      <c r="BH12"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
+      <c r="BK12"/>
+      <c r="BL12"/>
+      <c r="BM12"/>
+      <c r="BN12"/>
+      <c r="BO12"/>
+      <c r="BP12"/>
+      <c r="BQ12"/>
+      <c r="BR12"/>
+      <c r="BS12"/>
+      <c r="BT12"/>
+      <c r="BU12"/>
+      <c r="BV12"/>
+      <c r="BW12"/>
+      <c r="BX12"/>
+      <c r="BY12"/>
+      <c r="BZ12"/>
+      <c r="CA12"/>
+      <c r="CB12"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="11" t="s">
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>0.24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>0.24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13">
+        <v>30</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13" t="s">
         <v>37</v>
       </c>
-      <c r="C13">
-        <v>0.2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13">
-        <v>0.24</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13">
-        <v>0.24</v>
-      </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13">
-        <v>30</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
-      </c>
       <c r="O13">
         <v>30</v>
       </c>
@@ -1310,7 +1996,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R13">
         <v>4</v>
@@ -1318,50 +2004,113 @@
       <c r="S13">
         <v>3</v>
       </c>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
+      <c r="AJ13"/>
+      <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13"/>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13"/>
+      <c r="BD13"/>
+      <c r="BE13"/>
+      <c r="BF13"/>
+      <c r="BG13"/>
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13"/>
+      <c r="BL13"/>
+      <c r="BM13"/>
+      <c r="BN13"/>
+      <c r="BO13"/>
+      <c r="BP13"/>
+      <c r="BQ13"/>
+      <c r="BR13"/>
+      <c r="BS13"/>
+      <c r="BT13"/>
+      <c r="BU13"/>
+      <c r="BV13"/>
+      <c r="BW13"/>
+      <c r="BX13"/>
+      <c r="BY13"/>
+      <c r="BZ13"/>
+      <c r="CA13"/>
+      <c r="CB13"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="11" t="s">
+    <row r="14">
+      <c r="A14" s="4"/>
+      <c r="B14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14">
+        <v>0.2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14">
+        <v>0.24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>0.24</v>
+      </c>
+      <c r="J14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14">
+        <v>30</v>
+      </c>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14">
+        <v>30</v>
+      </c>
+      <c r="P14">
+        <v>30</v>
+      </c>
+      <c r="Q14" t="s">
         <v>38</v>
-      </c>
-      <c r="C14">
-        <v>0.2</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14">
-        <v>0.24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.81</v>
-      </c>
-      <c r="H14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14">
-        <v>0.24</v>
-      </c>
-      <c r="J14" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14">
-        <v>30</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14">
-        <v>30</v>
-      </c>
-      <c r="P14">
-        <v>30</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>33</v>
       </c>
       <c r="R14">
         <v>4</v>
@@ -1369,41 +2118,104 @@
       <c r="S14">
         <v>3</v>
       </c>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14"/>
+      <c r="AJ14"/>
+      <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14"/>
+      <c r="BD14"/>
+      <c r="BE14"/>
+      <c r="BF14"/>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
+      <c r="BL14"/>
+      <c r="BM14"/>
+      <c r="BN14"/>
+      <c r="BO14"/>
+      <c r="BP14"/>
+      <c r="BQ14"/>
+      <c r="BR14"/>
+      <c r="BS14"/>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
+      <c r="BY14"/>
+      <c r="BZ14"/>
+      <c r="CA14"/>
+      <c r="CB14"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="11" t="s">
-        <v>39</v>
+    <row r="15">
+      <c r="A15" s="4"/>
+      <c r="B15" s="41" t="s">
+        <v>47</v>
       </c>
       <c r="C15">
         <v>0.2</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>0.24</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0.78</v>
+        <v>48</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I15">
         <v>0.24</v>
       </c>
       <c r="J15" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K15">
         <v>30</v>
       </c>
+      <c r="L15"/>
+      <c r="M15"/>
       <c r="N15" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O15">
         <v>30</v>
@@ -1412,7 +2224,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R15">
         <v>4</v>
@@ -1420,41 +2232,104 @@
       <c r="S15">
         <v>3</v>
       </c>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
+      <c r="AI15"/>
+      <c r="AJ15"/>
+      <c r="AK15"/>
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
+      <c r="AU15"/>
+      <c r="AV15"/>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+      <c r="BA15"/>
+      <c r="BB15"/>
+      <c r="BC15"/>
+      <c r="BD15"/>
+      <c r="BE15"/>
+      <c r="BF15"/>
+      <c r="BG15"/>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
+      <c r="BK15"/>
+      <c r="BL15"/>
+      <c r="BM15"/>
+      <c r="BN15"/>
+      <c r="BO15"/>
+      <c r="BP15"/>
+      <c r="BQ15"/>
+      <c r="BR15"/>
+      <c r="BS15"/>
+      <c r="BT15"/>
+      <c r="BU15"/>
+      <c r="BV15"/>
+      <c r="BW15"/>
+      <c r="BX15"/>
+      <c r="BY15"/>
+      <c r="BZ15"/>
+      <c r="CA15"/>
+      <c r="CB15"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
+    <row r="16">
+      <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>0.2</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>0.24</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0.78</v>
+        <v>50</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I16">
         <v>0.24</v>
       </c>
       <c r="J16" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K16">
         <v>30</v>
       </c>
+      <c r="L16"/>
+      <c r="M16"/>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O16">
         <v>30</v>
@@ -1463,7 +2338,7 @@
         <v>30</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R16">
         <v>4</v>
@@ -1471,41 +2346,104 @@
       <c r="S16">
         <v>3</v>
       </c>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
+      <c r="AJ16"/>
+      <c r="AK16"/>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
+      <c r="AS16"/>
+      <c r="AT16"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16"/>
+      <c r="AX16"/>
+      <c r="AY16"/>
+      <c r="AZ16"/>
+      <c r="BA16"/>
+      <c r="BB16"/>
+      <c r="BC16"/>
+      <c r="BD16"/>
+      <c r="BE16"/>
+      <c r="BF16"/>
+      <c r="BG16"/>
+      <c r="BH16"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
+      <c r="BN16"/>
+      <c r="BO16"/>
+      <c r="BP16"/>
+      <c r="BQ16"/>
+      <c r="BR16"/>
+      <c r="BS16"/>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
+      <c r="BX16"/>
+      <c r="BY16"/>
+      <c r="BZ16"/>
+      <c r="CA16"/>
+      <c r="CB16"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
+    <row r="17">
+      <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C17">
         <v>0.2</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0.24</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0.91</v>
+        <v>52</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I17">
         <v>0.24</v>
       </c>
       <c r="J17" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K17">
         <v>30</v>
       </c>
+      <c r="L17"/>
+      <c r="M17"/>
       <c r="N17" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O17">
         <v>30</v>
@@ -1514,7 +2452,7 @@
         <v>30</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R17">
         <v>4</v>
@@ -1522,41 +2460,104 @@
       <c r="S17">
         <v>3</v>
       </c>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17"/>
+      <c r="AI17"/>
+      <c r="AJ17"/>
+      <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17"/>
+      <c r="AS17"/>
+      <c r="AT17"/>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17"/>
+      <c r="AX17"/>
+      <c r="AY17"/>
+      <c r="AZ17"/>
+      <c r="BA17"/>
+      <c r="BB17"/>
+      <c r="BC17"/>
+      <c r="BD17"/>
+      <c r="BE17"/>
+      <c r="BF17"/>
+      <c r="BG17"/>
+      <c r="BH17"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
+      <c r="BK17"/>
+      <c r="BL17"/>
+      <c r="BM17"/>
+      <c r="BN17"/>
+      <c r="BO17"/>
+      <c r="BP17"/>
+      <c r="BQ17"/>
+      <c r="BR17"/>
+      <c r="BS17"/>
+      <c r="BT17"/>
+      <c r="BU17"/>
+      <c r="BV17"/>
+      <c r="BW17"/>
+      <c r="BX17"/>
+      <c r="BY17"/>
+      <c r="BZ17"/>
+      <c r="CA17"/>
+      <c r="CB17"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
+    <row r="18">
+      <c r="A18" s="4"/>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <v>0.2</v>
       </c>
       <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18">
+        <v>0.24</v>
+      </c>
+      <c r="F18" t="s">
         <v>54</v>
       </c>
-      <c r="E18">
-        <v>0.24</v>
-      </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="10">
-        <v>0.88</v>
+      <c r="G18" s="42" t="n">
+        <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I18">
         <v>0.24</v>
       </c>
       <c r="J18" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K18">
         <v>30</v>
       </c>
+      <c r="L18"/>
+      <c r="M18"/>
       <c r="N18" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O18">
         <v>30</v>
@@ -1565,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R18">
         <v>4</v>
@@ -1573,41 +2574,104 @@
       <c r="S18">
         <v>3</v>
       </c>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18"/>
+      <c r="AG18"/>
+      <c r="AH18"/>
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18"/>
+      <c r="BD18"/>
+      <c r="BE18"/>
+      <c r="BF18"/>
+      <c r="BG18"/>
+      <c r="BH18"/>
+      <c r="BI18"/>
+      <c r="BJ18"/>
+      <c r="BK18"/>
+      <c r="BL18"/>
+      <c r="BM18"/>
+      <c r="BN18"/>
+      <c r="BO18"/>
+      <c r="BP18"/>
+      <c r="BQ18"/>
+      <c r="BR18"/>
+      <c r="BS18"/>
+      <c r="BT18"/>
+      <c r="BU18"/>
+      <c r="BV18"/>
+      <c r="BW18"/>
+      <c r="BX18"/>
+      <c r="BY18"/>
+      <c r="BZ18"/>
+      <c r="CA18"/>
+      <c r="CB18"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
+    <row r="19">
+      <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C19">
         <v>0.2</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>0.24</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="10">
-        <v>0.85</v>
+        <v>56</v>
+      </c>
+      <c r="G19" s="42" t="n">
+        <v>85</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I19">
         <v>0.24</v>
       </c>
       <c r="J19" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K19">
         <v>30</v>
       </c>
+      <c r="L19"/>
+      <c r="M19"/>
       <c r="N19" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O19">
         <v>30</v>
@@ -1616,7 +2680,7 @@
         <v>30</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -1624,41 +2688,104 @@
       <c r="S19">
         <v>3</v>
       </c>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+      <c r="AF19"/>
+      <c r="AG19"/>
+      <c r="AH19"/>
+      <c r="AI19"/>
+      <c r="AJ19"/>
+      <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
+      <c r="AS19"/>
+      <c r="AT19"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
+      <c r="AZ19"/>
+      <c r="BA19"/>
+      <c r="BB19"/>
+      <c r="BC19"/>
+      <c r="BD19"/>
+      <c r="BE19"/>
+      <c r="BF19"/>
+      <c r="BG19"/>
+      <c r="BH19"/>
+      <c r="BI19"/>
+      <c r="BJ19"/>
+      <c r="BK19"/>
+      <c r="BL19"/>
+      <c r="BM19"/>
+      <c r="BN19"/>
+      <c r="BO19"/>
+      <c r="BP19"/>
+      <c r="BQ19"/>
+      <c r="BR19"/>
+      <c r="BS19"/>
+      <c r="BT19"/>
+      <c r="BU19"/>
+      <c r="BV19"/>
+      <c r="BW19"/>
+      <c r="BX19"/>
+      <c r="BY19"/>
+      <c r="BZ19"/>
+      <c r="CA19"/>
+      <c r="CB19"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
+    <row r="20">
+      <c r="A20" s="4"/>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C20">
         <v>0.2</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>0.24</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="10">
-        <v>0.83</v>
+        <v>58</v>
+      </c>
+      <c r="G20" s="42" t="n">
+        <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I20">
         <v>0.24</v>
       </c>
       <c r="J20" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K20">
         <v>30</v>
       </c>
+      <c r="L20"/>
+      <c r="M20"/>
       <c r="N20" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O20">
         <v>30</v>
@@ -1667,7 +2794,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R20">
         <v>4</v>
@@ -1675,41 +2802,104 @@
       <c r="S20">
         <v>3</v>
       </c>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20"/>
+      <c r="AF20"/>
+      <c r="AG20"/>
+      <c r="AH20"/>
+      <c r="AI20"/>
+      <c r="AJ20"/>
+      <c r="AK20"/>
+      <c r="AL20"/>
+      <c r="AM20"/>
+      <c r="AN20"/>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20"/>
+      <c r="AS20"/>
+      <c r="AT20"/>
+      <c r="AU20"/>
+      <c r="AV20"/>
+      <c r="AW20"/>
+      <c r="AX20"/>
+      <c r="AY20"/>
+      <c r="AZ20"/>
+      <c r="BA20"/>
+      <c r="BB20"/>
+      <c r="BC20"/>
+      <c r="BD20"/>
+      <c r="BE20"/>
+      <c r="BF20"/>
+      <c r="BG20"/>
+      <c r="BH20"/>
+      <c r="BI20"/>
+      <c r="BJ20"/>
+      <c r="BK20"/>
+      <c r="BL20"/>
+      <c r="BM20"/>
+      <c r="BN20"/>
+      <c r="BO20"/>
+      <c r="BP20"/>
+      <c r="BQ20"/>
+      <c r="BR20"/>
+      <c r="BS20"/>
+      <c r="BT20"/>
+      <c r="BU20"/>
+      <c r="BV20"/>
+      <c r="BW20"/>
+      <c r="BX20"/>
+      <c r="BY20"/>
+      <c r="BZ20"/>
+      <c r="CA20"/>
+      <c r="CB20"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
+    <row r="21">
+      <c r="A21" s="4"/>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>0.2</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E21">
         <v>0.24</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="10">
-        <v>0.85</v>
+        <v>60</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>85</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I21">
         <v>0.24</v>
       </c>
       <c r="J21" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K21">
         <v>30</v>
       </c>
+      <c r="L21"/>
+      <c r="M21"/>
       <c r="N21" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O21">
         <v>30</v>
@@ -1718,7 +2908,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R21">
         <v>4</v>
@@ -1726,41 +2916,104 @@
       <c r="S21">
         <v>3</v>
       </c>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21"/>
+      <c r="AF21"/>
+      <c r="AG21"/>
+      <c r="AH21"/>
+      <c r="AI21"/>
+      <c r="AJ21"/>
+      <c r="AK21"/>
+      <c r="AL21"/>
+      <c r="AM21"/>
+      <c r="AN21"/>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21"/>
+      <c r="AS21"/>
+      <c r="AT21"/>
+      <c r="AU21"/>
+      <c r="AV21"/>
+      <c r="AW21"/>
+      <c r="AX21"/>
+      <c r="AY21"/>
+      <c r="AZ21"/>
+      <c r="BA21"/>
+      <c r="BB21"/>
+      <c r="BC21"/>
+      <c r="BD21"/>
+      <c r="BE21"/>
+      <c r="BF21"/>
+      <c r="BG21"/>
+      <c r="BH21"/>
+      <c r="BI21"/>
+      <c r="BJ21"/>
+      <c r="BK21"/>
+      <c r="BL21"/>
+      <c r="BM21"/>
+      <c r="BN21"/>
+      <c r="BO21"/>
+      <c r="BP21"/>
+      <c r="BQ21"/>
+      <c r="BR21"/>
+      <c r="BS21"/>
+      <c r="BT21"/>
+      <c r="BU21"/>
+      <c r="BV21"/>
+      <c r="BW21"/>
+      <c r="BX21"/>
+      <c r="BY21"/>
+      <c r="BZ21"/>
+      <c r="CA21"/>
+      <c r="CB21"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
+    <row r="22">
+      <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C22">
         <v>0.2</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E22">
         <v>0.24</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="10">
-        <v>0.81</v>
+        <v>62</v>
+      </c>
+      <c r="G22" s="42" t="n">
+        <v>81</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I22">
         <v>0.24</v>
       </c>
       <c r="J22" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K22">
         <v>30</v>
       </c>
+      <c r="L22"/>
+      <c r="M22"/>
       <c r="N22" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O22">
         <v>30</v>
@@ -1769,7 +3022,7 @@
         <v>30</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R22">
         <v>4</v>
@@ -1777,41 +3030,104 @@
       <c r="S22">
         <v>3</v>
       </c>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22"/>
+      <c r="BD22"/>
+      <c r="BE22"/>
+      <c r="BF22"/>
+      <c r="BG22"/>
+      <c r="BH22"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
+      <c r="BK22"/>
+      <c r="BL22"/>
+      <c r="BM22"/>
+      <c r="BN22"/>
+      <c r="BO22"/>
+      <c r="BP22"/>
+      <c r="BQ22"/>
+      <c r="BR22"/>
+      <c r="BS22"/>
+      <c r="BT22"/>
+      <c r="BU22"/>
+      <c r="BV22"/>
+      <c r="BW22"/>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
+    <row r="23">
+      <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>0.2</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E23">
         <v>0.24</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0.9</v>
+        <v>64</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>90</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I23">
         <v>0.24</v>
       </c>
       <c r="J23" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K23">
         <v>30</v>
       </c>
+      <c r="L23"/>
+      <c r="M23"/>
       <c r="N23" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O23">
         <v>30</v>
@@ -1820,7 +3136,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R23">
         <v>4</v>
@@ -1828,41 +3144,104 @@
       <c r="S23">
         <v>3</v>
       </c>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23"/>
+      <c r="BD23"/>
+      <c r="BE23"/>
+      <c r="BF23"/>
+      <c r="BG23"/>
+      <c r="BH23"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
+      <c r="BK23"/>
+      <c r="BL23"/>
+      <c r="BM23"/>
+      <c r="BN23"/>
+      <c r="BO23"/>
+      <c r="BP23"/>
+      <c r="BQ23"/>
+      <c r="BR23"/>
+      <c r="BS23"/>
+      <c r="BT23"/>
+      <c r="BU23"/>
+      <c r="BV23"/>
+      <c r="BW23"/>
+      <c r="BX23"/>
+      <c r="BY23"/>
+      <c r="BZ23"/>
+      <c r="CA23"/>
+      <c r="CB23"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
+    <row r="24">
+      <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C24">
         <v>0.2</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E24">
         <v>0.24</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="10">
-        <v>0.83</v>
+        <v>66</v>
+      </c>
+      <c r="G24" s="42" t="n">
+        <v>83</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I24">
         <v>0.24</v>
       </c>
       <c r="J24" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K24">
         <v>30</v>
       </c>
+      <c r="L24"/>
+      <c r="M24"/>
       <c r="N24" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O24">
         <v>30</v>
@@ -1871,7 +3250,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R24">
         <v>4</v>
@@ -1879,41 +3258,104 @@
       <c r="S24">
         <v>3</v>
       </c>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24"/>
+      <c r="AF24"/>
+      <c r="AG24"/>
+      <c r="AH24"/>
+      <c r="AI24"/>
+      <c r="AJ24"/>
+      <c r="AK24"/>
+      <c r="AL24"/>
+      <c r="AM24"/>
+      <c r="AN24"/>
+      <c r="AO24"/>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24"/>
+      <c r="AS24"/>
+      <c r="AT24"/>
+      <c r="AU24"/>
+      <c r="AV24"/>
+      <c r="AW24"/>
+      <c r="AX24"/>
+      <c r="AY24"/>
+      <c r="AZ24"/>
+      <c r="BA24"/>
+      <c r="BB24"/>
+      <c r="BC24"/>
+      <c r="BD24"/>
+      <c r="BE24"/>
+      <c r="BF24"/>
+      <c r="BG24"/>
+      <c r="BH24"/>
+      <c r="BI24"/>
+      <c r="BJ24"/>
+      <c r="BK24"/>
+      <c r="BL24"/>
+      <c r="BM24"/>
+      <c r="BN24"/>
+      <c r="BO24"/>
+      <c r="BP24"/>
+      <c r="BQ24"/>
+      <c r="BR24"/>
+      <c r="BS24"/>
+      <c r="BT24"/>
+      <c r="BU24"/>
+      <c r="BV24"/>
+      <c r="BW24"/>
+      <c r="BX24"/>
+      <c r="BY24"/>
+      <c r="BZ24"/>
+      <c r="CA24"/>
+      <c r="CB24"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
+    <row r="25">
+      <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>0.2</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E25">
         <v>0.24</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0.91</v>
+        <v>68</v>
+      </c>
+      <c r="G25" s="42" t="n">
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I25">
         <v>0.24</v>
       </c>
       <c r="J25" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K25">
         <v>30</v>
       </c>
+      <c r="L25"/>
+      <c r="M25"/>
       <c r="N25" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O25">
         <v>30</v>
@@ -1922,7 +3364,7 @@
         <v>30</v>
       </c>
       <c r="Q25" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R25">
         <v>4</v>
@@ -1930,41 +3372,104 @@
       <c r="S25">
         <v>3</v>
       </c>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25"/>
+      <c r="AF25"/>
+      <c r="AG25"/>
+      <c r="AH25"/>
+      <c r="AI25"/>
+      <c r="AJ25"/>
+      <c r="AK25"/>
+      <c r="AL25"/>
+      <c r="AM25"/>
+      <c r="AN25"/>
+      <c r="AO25"/>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25"/>
+      <c r="AS25"/>
+      <c r="AT25"/>
+      <c r="AU25"/>
+      <c r="AV25"/>
+      <c r="AW25"/>
+      <c r="AX25"/>
+      <c r="AY25"/>
+      <c r="AZ25"/>
+      <c r="BA25"/>
+      <c r="BB25"/>
+      <c r="BC25"/>
+      <c r="BD25"/>
+      <c r="BE25"/>
+      <c r="BF25"/>
+      <c r="BG25"/>
+      <c r="BH25"/>
+      <c r="BI25"/>
+      <c r="BJ25"/>
+      <c r="BK25"/>
+      <c r="BL25"/>
+      <c r="BM25"/>
+      <c r="BN25"/>
+      <c r="BO25"/>
+      <c r="BP25"/>
+      <c r="BQ25"/>
+      <c r="BR25"/>
+      <c r="BS25"/>
+      <c r="BT25"/>
+      <c r="BU25"/>
+      <c r="BV25"/>
+      <c r="BW25"/>
+      <c r="BX25"/>
+      <c r="BY25"/>
+      <c r="BZ25"/>
+      <c r="CA25"/>
+      <c r="CB25"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
+    <row r="26">
+      <c r="A26" s="4"/>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C26">
         <v>0.2</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E26">
         <v>0.24</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26" s="10">
-        <v>0.85</v>
+        <v>70</v>
+      </c>
+      <c r="G26" s="42" t="n">
+        <v>85</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I26">
         <v>0.24</v>
       </c>
       <c r="J26" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K26">
         <v>30</v>
       </c>
+      <c r="L26"/>
+      <c r="M26"/>
       <c r="N26" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O26">
         <v>30</v>
@@ -1973,7 +3478,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R26">
         <v>4</v>
@@ -1981,41 +3486,104 @@
       <c r="S26">
         <v>3</v>
       </c>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26"/>
+      <c r="AA26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
+      <c r="AF26"/>
+      <c r="AG26"/>
+      <c r="AH26"/>
+      <c r="AI26"/>
+      <c r="AJ26"/>
+      <c r="AK26"/>
+      <c r="AL26"/>
+      <c r="AM26"/>
+      <c r="AN26"/>
+      <c r="AO26"/>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26"/>
+      <c r="AS26"/>
+      <c r="AT26"/>
+      <c r="AU26"/>
+      <c r="AV26"/>
+      <c r="AW26"/>
+      <c r="AX26"/>
+      <c r="AY26"/>
+      <c r="AZ26"/>
+      <c r="BA26"/>
+      <c r="BB26"/>
+      <c r="BC26"/>
+      <c r="BD26"/>
+      <c r="BE26"/>
+      <c r="BF26"/>
+      <c r="BG26"/>
+      <c r="BH26"/>
+      <c r="BI26"/>
+      <c r="BJ26"/>
+      <c r="BK26"/>
+      <c r="BL26"/>
+      <c r="BM26"/>
+      <c r="BN26"/>
+      <c r="BO26"/>
+      <c r="BP26"/>
+      <c r="BQ26"/>
+      <c r="BR26"/>
+      <c r="BS26"/>
+      <c r="BT26"/>
+      <c r="BU26"/>
+      <c r="BV26"/>
+      <c r="BW26"/>
+      <c r="BX26"/>
+      <c r="BY26"/>
+      <c r="BZ26"/>
+      <c r="CA26"/>
+      <c r="CB26"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
+    <row r="27">
+      <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C27">
         <v>0.2</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E27">
         <v>0.24</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="10">
-        <v>0.81</v>
+        <v>73</v>
+      </c>
+      <c r="G27" s="42" t="n">
+        <v>81</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I27">
         <v>0.24</v>
       </c>
       <c r="J27" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K27">
         <v>30</v>
       </c>
+      <c r="L27"/>
+      <c r="M27"/>
       <c r="N27" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O27">
         <v>30</v>
@@ -2024,7 +3592,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R27">
         <v>4</v>
@@ -2032,41 +3600,104 @@
       <c r="S27">
         <v>3</v>
       </c>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27"/>
+      <c r="AF27"/>
+      <c r="AG27"/>
+      <c r="AH27"/>
+      <c r="AI27"/>
+      <c r="AJ27"/>
+      <c r="AK27"/>
+      <c r="AL27"/>
+      <c r="AM27"/>
+      <c r="AN27"/>
+      <c r="AO27"/>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27"/>
+      <c r="AS27"/>
+      <c r="AT27"/>
+      <c r="AU27"/>
+      <c r="AV27"/>
+      <c r="AW27"/>
+      <c r="AX27"/>
+      <c r="AY27"/>
+      <c r="AZ27"/>
+      <c r="BA27"/>
+      <c r="BB27"/>
+      <c r="BC27"/>
+      <c r="BD27"/>
+      <c r="BE27"/>
+      <c r="BF27"/>
+      <c r="BG27"/>
+      <c r="BH27"/>
+      <c r="BI27"/>
+      <c r="BJ27"/>
+      <c r="BK27"/>
+      <c r="BL27"/>
+      <c r="BM27"/>
+      <c r="BN27"/>
+      <c r="BO27"/>
+      <c r="BP27"/>
+      <c r="BQ27"/>
+      <c r="BR27"/>
+      <c r="BS27"/>
+      <c r="BT27"/>
+      <c r="BU27"/>
+      <c r="BV27"/>
+      <c r="BW27"/>
+      <c r="BX27"/>
+      <c r="BY27"/>
+      <c r="BZ27"/>
+      <c r="CA27"/>
+      <c r="CB27"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
+    <row r="28">
+      <c r="A28" s="4"/>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C28">
         <v>0.2</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E28">
         <v>0.24</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="10">
-        <v>0.9</v>
+        <v>75</v>
+      </c>
+      <c r="G28" s="42" t="n">
+        <v>90</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I28">
         <v>0.24</v>
       </c>
       <c r="J28" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K28">
         <v>30</v>
       </c>
+      <c r="L28"/>
+      <c r="M28"/>
       <c r="N28" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O28">
         <v>30</v>
@@ -2075,7 +3706,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R28">
         <v>4</v>
@@ -2083,41 +3714,104 @@
       <c r="S28">
         <v>3</v>
       </c>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28"/>
+      <c r="AF28"/>
+      <c r="AG28"/>
+      <c r="AH28"/>
+      <c r="AI28"/>
+      <c r="AJ28"/>
+      <c r="AK28"/>
+      <c r="AL28"/>
+      <c r="AM28"/>
+      <c r="AN28"/>
+      <c r="AO28"/>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28"/>
+      <c r="AS28"/>
+      <c r="AT28"/>
+      <c r="AU28"/>
+      <c r="AV28"/>
+      <c r="AW28"/>
+      <c r="AX28"/>
+      <c r="AY28"/>
+      <c r="AZ28"/>
+      <c r="BA28"/>
+      <c r="BB28"/>
+      <c r="BC28"/>
+      <c r="BD28"/>
+      <c r="BE28"/>
+      <c r="BF28"/>
+      <c r="BG28"/>
+      <c r="BH28"/>
+      <c r="BI28"/>
+      <c r="BJ28"/>
+      <c r="BK28"/>
+      <c r="BL28"/>
+      <c r="BM28"/>
+      <c r="BN28"/>
+      <c r="BO28"/>
+      <c r="BP28"/>
+      <c r="BQ28"/>
+      <c r="BR28"/>
+      <c r="BS28"/>
+      <c r="BT28"/>
+      <c r="BU28"/>
+      <c r="BV28"/>
+      <c r="BW28"/>
+      <c r="BX28"/>
+      <c r="BY28"/>
+      <c r="BZ28"/>
+      <c r="CA28"/>
+      <c r="CB28"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
+    <row r="29">
+      <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C29">
         <v>0.2</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E29">
         <v>0.24</v>
       </c>
       <c r="F29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="42" t="n">
         <v>89</v>
       </c>
-      <c r="G29" s="10">
-        <v>0.89</v>
-      </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I29">
         <v>0.24</v>
       </c>
       <c r="J29" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K29">
         <v>30</v>
       </c>
+      <c r="L29"/>
+      <c r="M29"/>
       <c r="N29" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O29">
         <v>30</v>
@@ -2126,7 +3820,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R29">
         <v>4</v>
@@ -2134,41 +3828,104 @@
       <c r="S29">
         <v>3</v>
       </c>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29"/>
+      <c r="AF29"/>
+      <c r="AG29"/>
+      <c r="AH29"/>
+      <c r="AI29"/>
+      <c r="AJ29"/>
+      <c r="AK29"/>
+      <c r="AL29"/>
+      <c r="AM29"/>
+      <c r="AN29"/>
+      <c r="AO29"/>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29"/>
+      <c r="AS29"/>
+      <c r="AT29"/>
+      <c r="AU29"/>
+      <c r="AV29"/>
+      <c r="AW29"/>
+      <c r="AX29"/>
+      <c r="AY29"/>
+      <c r="AZ29"/>
+      <c r="BA29"/>
+      <c r="BB29"/>
+      <c r="BC29"/>
+      <c r="BD29"/>
+      <c r="BE29"/>
+      <c r="BF29"/>
+      <c r="BG29"/>
+      <c r="BH29"/>
+      <c r="BI29"/>
+      <c r="BJ29"/>
+      <c r="BK29"/>
+      <c r="BL29"/>
+      <c r="BM29"/>
+      <c r="BN29"/>
+      <c r="BO29"/>
+      <c r="BP29"/>
+      <c r="BQ29"/>
+      <c r="BR29"/>
+      <c r="BS29"/>
+      <c r="BT29"/>
+      <c r="BU29"/>
+      <c r="BV29"/>
+      <c r="BW29"/>
+      <c r="BX29"/>
+      <c r="BY29"/>
+      <c r="BZ29"/>
+      <c r="CA29"/>
+      <c r="CB29"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
+    <row r="30">
+      <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>0.2</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E30">
         <v>0.24</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.88</v>
+        <v>79</v>
+      </c>
+      <c r="G30" s="42" t="n">
+        <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I30">
         <v>0.24</v>
       </c>
       <c r="J30" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K30">
         <v>30</v>
       </c>
+      <c r="L30"/>
+      <c r="M30"/>
       <c r="N30" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O30">
         <v>30</v>
@@ -2177,7 +3934,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R30">
         <v>4</v>
@@ -2185,41 +3942,104 @@
       <c r="S30">
         <v>3</v>
       </c>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
+      <c r="AG30"/>
+      <c r="AH30"/>
+      <c r="AI30"/>
+      <c r="AJ30"/>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
+      <c r="AS30"/>
+      <c r="AT30"/>
+      <c r="AU30"/>
+      <c r="AV30"/>
+      <c r="AW30"/>
+      <c r="AX30"/>
+      <c r="AY30"/>
+      <c r="AZ30"/>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30"/>
+      <c r="BD30"/>
+      <c r="BE30"/>
+      <c r="BF30"/>
+      <c r="BG30"/>
+      <c r="BH30"/>
+      <c r="BI30"/>
+      <c r="BJ30"/>
+      <c r="BK30"/>
+      <c r="BL30"/>
+      <c r="BM30"/>
+      <c r="BN30"/>
+      <c r="BO30"/>
+      <c r="BP30"/>
+      <c r="BQ30"/>
+      <c r="BR30"/>
+      <c r="BS30"/>
+      <c r="BT30"/>
+      <c r="BU30"/>
+      <c r="BV30"/>
+      <c r="BW30"/>
+      <c r="BX30"/>
+      <c r="BY30"/>
+      <c r="BZ30"/>
+      <c r="CA30"/>
+      <c r="CB30"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
+    <row r="31">
+      <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C31">
         <v>0.2</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E31">
         <v>0.24</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0.84</v>
+        <v>81</v>
+      </c>
+      <c r="G31" s="42" t="n">
+        <v>84</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I31">
         <v>0.24</v>
       </c>
       <c r="J31" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K31">
         <v>30</v>
       </c>
+      <c r="L31"/>
+      <c r="M31"/>
       <c r="N31" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O31">
         <v>30</v>
@@ -2228,7 +4048,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R31">
         <v>4</v>
@@ -2236,41 +4056,104 @@
       <c r="S31">
         <v>3</v>
       </c>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
+      <c r="AF31"/>
+      <c r="AG31"/>
+      <c r="AH31"/>
+      <c r="AI31"/>
+      <c r="AJ31"/>
+      <c r="AK31"/>
+      <c r="AL31"/>
+      <c r="AM31"/>
+      <c r="AN31"/>
+      <c r="AO31"/>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+      <c r="AR31"/>
+      <c r="AS31"/>
+      <c r="AT31"/>
+      <c r="AU31"/>
+      <c r="AV31"/>
+      <c r="AW31"/>
+      <c r="AX31"/>
+      <c r="AY31"/>
+      <c r="AZ31"/>
+      <c r="BA31"/>
+      <c r="BB31"/>
+      <c r="BC31"/>
+      <c r="BD31"/>
+      <c r="BE31"/>
+      <c r="BF31"/>
+      <c r="BG31"/>
+      <c r="BH31"/>
+      <c r="BI31"/>
+      <c r="BJ31"/>
+      <c r="BK31"/>
+      <c r="BL31"/>
+      <c r="BM31"/>
+      <c r="BN31"/>
+      <c r="BO31"/>
+      <c r="BP31"/>
+      <c r="BQ31"/>
+      <c r="BR31"/>
+      <c r="BS31"/>
+      <c r="BT31"/>
+      <c r="BU31"/>
+      <c r="BV31"/>
+      <c r="BW31"/>
+      <c r="BX31"/>
+      <c r="BY31"/>
+      <c r="BZ31"/>
+      <c r="CA31"/>
+      <c r="CB31"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
+    <row r="32">
+      <c r="A32" s="4"/>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C32">
         <v>0.2</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E32">
         <v>0.24</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.9</v>
+        <v>83</v>
+      </c>
+      <c r="G32" s="42" t="n">
+        <v>90</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I32">
         <v>0.24</v>
       </c>
       <c r="J32" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K32">
         <v>30</v>
       </c>
+      <c r="L32"/>
+      <c r="M32"/>
       <c r="N32" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O32">
         <v>30</v>
@@ -2279,7 +4162,7 @@
         <v>30</v>
       </c>
       <c r="Q32" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R32">
         <v>4</v>
@@ -2287,41 +4170,104 @@
       <c r="S32">
         <v>3</v>
       </c>
+      <c r="T32"/>
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32"/>
+      <c r="Z32"/>
+      <c r="AA32"/>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
+      <c r="AF32"/>
+      <c r="AG32"/>
+      <c r="AH32"/>
+      <c r="AI32"/>
+      <c r="AJ32"/>
+      <c r="AK32"/>
+      <c r="AL32"/>
+      <c r="AM32"/>
+      <c r="AN32"/>
+      <c r="AO32"/>
+      <c r="AP32"/>
+      <c r="AQ32"/>
+      <c r="AR32"/>
+      <c r="AS32"/>
+      <c r="AT32"/>
+      <c r="AU32"/>
+      <c r="AV32"/>
+      <c r="AW32"/>
+      <c r="AX32"/>
+      <c r="AY32"/>
+      <c r="AZ32"/>
+      <c r="BA32"/>
+      <c r="BB32"/>
+      <c r="BC32"/>
+      <c r="BD32"/>
+      <c r="BE32"/>
+      <c r="BF32"/>
+      <c r="BG32"/>
+      <c r="BH32"/>
+      <c r="BI32"/>
+      <c r="BJ32"/>
+      <c r="BK32"/>
+      <c r="BL32"/>
+      <c r="BM32"/>
+      <c r="BN32"/>
+      <c r="BO32"/>
+      <c r="BP32"/>
+      <c r="BQ32"/>
+      <c r="BR32"/>
+      <c r="BS32"/>
+      <c r="BT32"/>
+      <c r="BU32"/>
+      <c r="BV32"/>
+      <c r="BW32"/>
+      <c r="BX32"/>
+      <c r="BY32"/>
+      <c r="BZ32"/>
+      <c r="CA32"/>
+      <c r="CB32"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
+    <row r="33">
+      <c r="A33" s="4"/>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C33">
         <v>0.2</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>0.24</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0.9</v>
+        <v>85</v>
+      </c>
+      <c r="G33" s="42" t="n">
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I33">
         <v>0.24</v>
       </c>
       <c r="J33" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K33">
         <v>30</v>
       </c>
+      <c r="L33"/>
+      <c r="M33"/>
       <c r="N33" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O33">
         <v>30</v>
@@ -2330,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="Q33" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R33">
         <v>4</v>
@@ -2338,41 +4284,104 @@
       <c r="S33">
         <v>3</v>
       </c>
+      <c r="T33"/>
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="Y33"/>
+      <c r="Z33"/>
+      <c r="AA33"/>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
+      <c r="AF33"/>
+      <c r="AG33"/>
+      <c r="AH33"/>
+      <c r="AI33"/>
+      <c r="AJ33"/>
+      <c r="AK33"/>
+      <c r="AL33"/>
+      <c r="AM33"/>
+      <c r="AN33"/>
+      <c r="AO33"/>
+      <c r="AP33"/>
+      <c r="AQ33"/>
+      <c r="AR33"/>
+      <c r="AS33"/>
+      <c r="AT33"/>
+      <c r="AU33"/>
+      <c r="AV33"/>
+      <c r="AW33"/>
+      <c r="AX33"/>
+      <c r="AY33"/>
+      <c r="AZ33"/>
+      <c r="BA33"/>
+      <c r="BB33"/>
+      <c r="BC33"/>
+      <c r="BD33"/>
+      <c r="BE33"/>
+      <c r="BF33"/>
+      <c r="BG33"/>
+      <c r="BH33"/>
+      <c r="BI33"/>
+      <c r="BJ33"/>
+      <c r="BK33"/>
+      <c r="BL33"/>
+      <c r="BM33"/>
+      <c r="BN33"/>
+      <c r="BO33"/>
+      <c r="BP33"/>
+      <c r="BQ33"/>
+      <c r="BR33"/>
+      <c r="BS33"/>
+      <c r="BT33"/>
+      <c r="BU33"/>
+      <c r="BV33"/>
+      <c r="BW33"/>
+      <c r="BX33"/>
+      <c r="BY33"/>
+      <c r="BZ33"/>
+      <c r="CA33"/>
+      <c r="CB33"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
+    <row r="34">
+      <c r="A34" s="4"/>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C34">
         <v>0.2</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>0.24</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
-      </c>
-      <c r="G34" s="10">
-        <v>0.91</v>
+        <v>87</v>
+      </c>
+      <c r="G34" s="42" t="n">
+        <v>91</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I34">
         <v>0.24</v>
       </c>
       <c r="J34" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K34">
         <v>30</v>
       </c>
+      <c r="L34"/>
+      <c r="M34"/>
       <c r="N34" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O34">
         <v>30</v>
@@ -2381,7 +4390,7 @@
         <v>30</v>
       </c>
       <c r="Q34" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R34">
         <v>4</v>
@@ -2389,41 +4398,104 @@
       <c r="S34">
         <v>3</v>
       </c>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34"/>
+      <c r="AF34"/>
+      <c r="AG34"/>
+      <c r="AH34"/>
+      <c r="AI34"/>
+      <c r="AJ34"/>
+      <c r="AK34"/>
+      <c r="AL34"/>
+      <c r="AM34"/>
+      <c r="AN34"/>
+      <c r="AO34"/>
+      <c r="AP34"/>
+      <c r="AQ34"/>
+      <c r="AR34"/>
+      <c r="AS34"/>
+      <c r="AT34"/>
+      <c r="AU34"/>
+      <c r="AV34"/>
+      <c r="AW34"/>
+      <c r="AX34"/>
+      <c r="AY34"/>
+      <c r="AZ34"/>
+      <c r="BA34"/>
+      <c r="BB34"/>
+      <c r="BC34"/>
+      <c r="BD34"/>
+      <c r="BE34"/>
+      <c r="BF34"/>
+      <c r="BG34"/>
+      <c r="BH34"/>
+      <c r="BI34"/>
+      <c r="BJ34"/>
+      <c r="BK34"/>
+      <c r="BL34"/>
+      <c r="BM34"/>
+      <c r="BN34"/>
+      <c r="BO34"/>
+      <c r="BP34"/>
+      <c r="BQ34"/>
+      <c r="BR34"/>
+      <c r="BS34"/>
+      <c r="BT34"/>
+      <c r="BU34"/>
+      <c r="BV34"/>
+      <c r="BW34"/>
+      <c r="BX34"/>
+      <c r="BY34"/>
+      <c r="BZ34"/>
+      <c r="CA34"/>
+      <c r="CB34"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
+    <row r="35">
+      <c r="A35" s="4"/>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C35">
         <v>0.2</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>0.24</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0.87</v>
+        <v>89</v>
+      </c>
+      <c r="G35" s="42" t="n">
+        <v>87</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I35">
         <v>0.24</v>
       </c>
       <c r="J35" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K35">
         <v>30</v>
       </c>
+      <c r="L35"/>
+      <c r="M35"/>
       <c r="N35" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O35">
         <v>30</v>
@@ -2432,7 +4504,7 @@
         <v>30</v>
       </c>
       <c r="Q35" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R35">
         <v>4</v>
@@ -2440,41 +4512,104 @@
       <c r="S35">
         <v>3</v>
       </c>
+      <c r="T35"/>
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+      <c r="Y35"/>
+      <c r="Z35"/>
+      <c r="AA35"/>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35"/>
+      <c r="AF35"/>
+      <c r="AG35"/>
+      <c r="AH35"/>
+      <c r="AI35"/>
+      <c r="AJ35"/>
+      <c r="AK35"/>
+      <c r="AL35"/>
+      <c r="AM35"/>
+      <c r="AN35"/>
+      <c r="AO35"/>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35"/>
+      <c r="AS35"/>
+      <c r="AT35"/>
+      <c r="AU35"/>
+      <c r="AV35"/>
+      <c r="AW35"/>
+      <c r="AX35"/>
+      <c r="AY35"/>
+      <c r="AZ35"/>
+      <c r="BA35"/>
+      <c r="BB35"/>
+      <c r="BC35"/>
+      <c r="BD35"/>
+      <c r="BE35"/>
+      <c r="BF35"/>
+      <c r="BG35"/>
+      <c r="BH35"/>
+      <c r="BI35"/>
+      <c r="BJ35"/>
+      <c r="BK35"/>
+      <c r="BL35"/>
+      <c r="BM35"/>
+      <c r="BN35"/>
+      <c r="BO35"/>
+      <c r="BP35"/>
+      <c r="BQ35"/>
+      <c r="BR35"/>
+      <c r="BS35"/>
+      <c r="BT35"/>
+      <c r="BU35"/>
+      <c r="BV35"/>
+      <c r="BW35"/>
+      <c r="BX35"/>
+      <c r="BY35"/>
+      <c r="BZ35"/>
+      <c r="CA35"/>
+      <c r="CB35"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A36" s="2"/>
+    <row r="36">
+      <c r="A36" s="4"/>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C36">
         <v>0.2</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E36">
         <v>0.24</v>
       </c>
       <c r="F36" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" s="10">
-        <v>0.9</v>
+        <v>91</v>
+      </c>
+      <c r="G36" s="42" t="n">
+        <v>90</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I36">
         <v>0.24</v>
       </c>
       <c r="J36" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K36">
         <v>30</v>
       </c>
+      <c r="L36"/>
+      <c r="M36"/>
       <c r="N36" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O36">
         <v>30</v>
@@ -2483,7 +4618,7 @@
         <v>30</v>
       </c>
       <c r="Q36" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R36">
         <v>4</v>
@@ -2491,47 +4626,108 @@
       <c r="S36">
         <v>3</v>
       </c>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36"/>
+      <c r="AF36"/>
+      <c r="AG36"/>
+      <c r="AH36"/>
+      <c r="AI36"/>
+      <c r="AJ36"/>
+      <c r="AK36"/>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36"/>
+      <c r="AO36"/>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36"/>
+      <c r="AS36"/>
+      <c r="AT36"/>
+      <c r="AU36"/>
+      <c r="AV36"/>
+      <c r="AW36"/>
+      <c r="AX36"/>
+      <c r="AY36"/>
+      <c r="AZ36"/>
+      <c r="BA36"/>
+      <c r="BB36"/>
+      <c r="BC36"/>
+      <c r="BD36"/>
+      <c r="BE36"/>
+      <c r="BF36"/>
+      <c r="BG36"/>
+      <c r="BH36"/>
+      <c r="BI36"/>
+      <c r="BJ36"/>
+      <c r="BK36"/>
+      <c r="BL36"/>
+      <c r="BM36"/>
+      <c r="BN36"/>
+      <c r="BO36"/>
+      <c r="BP36"/>
+      <c r="BQ36"/>
+      <c r="BR36"/>
+      <c r="BS36"/>
+      <c r="BT36"/>
+      <c r="BU36"/>
+      <c r="BV36"/>
+      <c r="BW36"/>
+      <c r="BX36"/>
+      <c r="BY36"/>
+      <c r="BZ36"/>
+      <c r="CA36"/>
+      <c r="CB36"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
+    <row r="37">
+      <c r="A37" s="4"/>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C37">
         <v>0.2</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E37">
         <v>0.24</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="10">
-        <v>0.83</v>
+        <v>92</v>
+      </c>
+      <c r="G37" s="42" t="n">
+        <v>83</v>
       </c>
       <c r="H37" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I37">
         <v>0.24</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K37">
         <v>30</v>
       </c>
       <c r="L37" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M37">
         <v>0.2</v>
       </c>
       <c r="N37" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O37">
         <v>30</v>
@@ -2540,7 +4736,7 @@
         <v>30</v>
       </c>
       <c r="Q37" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R37">
         <v>4</v>
@@ -2548,47 +4744,108 @@
       <c r="S37">
         <v>3</v>
       </c>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+      <c r="AF37"/>
+      <c r="AG37"/>
+      <c r="AH37"/>
+      <c r="AI37"/>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
+      <c r="AN37"/>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
+      <c r="AS37"/>
+      <c r="AT37"/>
+      <c r="AU37"/>
+      <c r="AV37"/>
+      <c r="AW37"/>
+      <c r="AX37"/>
+      <c r="AY37"/>
+      <c r="AZ37"/>
+      <c r="BA37"/>
+      <c r="BB37"/>
+      <c r="BC37"/>
+      <c r="BD37"/>
+      <c r="BE37"/>
+      <c r="BF37"/>
+      <c r="BG37"/>
+      <c r="BH37"/>
+      <c r="BI37"/>
+      <c r="BJ37"/>
+      <c r="BK37"/>
+      <c r="BL37"/>
+      <c r="BM37"/>
+      <c r="BN37"/>
+      <c r="BO37"/>
+      <c r="BP37"/>
+      <c r="BQ37"/>
+      <c r="BR37"/>
+      <c r="BS37"/>
+      <c r="BT37"/>
+      <c r="BU37"/>
+      <c r="BV37"/>
+      <c r="BW37"/>
+      <c r="BX37"/>
+      <c r="BY37"/>
+      <c r="BZ37"/>
+      <c r="CA37"/>
+      <c r="CB37"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
+    <row r="38">
+      <c r="A38" s="4"/>
       <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38">
+        <v>0.2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38">
+        <v>0.24</v>
+      </c>
+      <c r="F38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" s="42" t="n">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s">
         <v>35</v>
       </c>
-      <c r="C38">
-        <v>0.2</v>
-      </c>
-      <c r="D38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38">
-        <v>0.24</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="10">
-        <v>0.78</v>
-      </c>
-      <c r="H38" t="s">
-        <v>30</v>
-      </c>
       <c r="I38">
         <v>0.24</v>
       </c>
       <c r="J38" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K38">
         <v>30</v>
       </c>
       <c r="L38" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M38">
         <v>0.2</v>
       </c>
       <c r="N38" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O38">
         <v>30</v>
@@ -2597,7 +4854,7 @@
         <v>30</v>
       </c>
       <c r="Q38" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R38">
         <v>4</v>
@@ -2605,47 +4862,108 @@
       <c r="S38">
         <v>3</v>
       </c>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38"/>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38"/>
+      <c r="AF38"/>
+      <c r="AG38"/>
+      <c r="AH38"/>
+      <c r="AI38"/>
+      <c r="AJ38"/>
+      <c r="AK38"/>
+      <c r="AL38"/>
+      <c r="AM38"/>
+      <c r="AN38"/>
+      <c r="AO38"/>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+      <c r="AR38"/>
+      <c r="AS38"/>
+      <c r="AT38"/>
+      <c r="AU38"/>
+      <c r="AV38"/>
+      <c r="AW38"/>
+      <c r="AX38"/>
+      <c r="AY38"/>
+      <c r="AZ38"/>
+      <c r="BA38"/>
+      <c r="BB38"/>
+      <c r="BC38"/>
+      <c r="BD38"/>
+      <c r="BE38"/>
+      <c r="BF38"/>
+      <c r="BG38"/>
+      <c r="BH38"/>
+      <c r="BI38"/>
+      <c r="BJ38"/>
+      <c r="BK38"/>
+      <c r="BL38"/>
+      <c r="BM38"/>
+      <c r="BN38"/>
+      <c r="BO38"/>
+      <c r="BP38"/>
+      <c r="BQ38"/>
+      <c r="BR38"/>
+      <c r="BS38"/>
+      <c r="BT38"/>
+      <c r="BU38"/>
+      <c r="BV38"/>
+      <c r="BW38"/>
+      <c r="BX38"/>
+      <c r="BY38"/>
+      <c r="BZ38"/>
+      <c r="CA38"/>
+      <c r="CB38"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
+    <row r="39">
+      <c r="A39" s="4"/>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C39">
         <v>0.2</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E39">
         <v>0.24</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
-      </c>
-      <c r="G39" s="10">
-        <v>0.76</v>
+        <v>96</v>
+      </c>
+      <c r="G39" s="42" t="n">
+        <v>76</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I39">
         <v>0.24</v>
       </c>
       <c r="J39" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K39">
         <v>30</v>
       </c>
       <c r="L39" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M39">
         <v>0.2</v>
       </c>
       <c r="N39" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O39">
         <v>30</v>
@@ -2654,7 +4972,7 @@
         <v>30</v>
       </c>
       <c r="Q39" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R39">
         <v>4</v>
@@ -2662,48 +4980,109 @@
       <c r="S39">
         <v>3</v>
       </c>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39"/>
+      <c r="AF39"/>
+      <c r="AG39"/>
+      <c r="AH39"/>
+      <c r="AI39"/>
+      <c r="AJ39"/>
+      <c r="AK39"/>
+      <c r="AL39"/>
+      <c r="AM39"/>
+      <c r="AN39"/>
+      <c r="AO39"/>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39"/>
+      <c r="AS39"/>
+      <c r="AT39"/>
+      <c r="AU39"/>
+      <c r="AV39"/>
+      <c r="AW39"/>
+      <c r="AX39"/>
+      <c r="AY39"/>
+      <c r="AZ39"/>
+      <c r="BA39"/>
+      <c r="BB39"/>
+      <c r="BC39"/>
+      <c r="BD39"/>
+      <c r="BE39"/>
+      <c r="BF39"/>
+      <c r="BG39"/>
+      <c r="BH39"/>
+      <c r="BI39"/>
+      <c r="BJ39"/>
+      <c r="BK39"/>
+      <c r="BL39"/>
+      <c r="BM39"/>
+      <c r="BN39"/>
+      <c r="BO39"/>
+      <c r="BP39"/>
+      <c r="BQ39"/>
+      <c r="BR39"/>
+      <c r="BS39"/>
+      <c r="BT39"/>
+      <c r="BU39"/>
+      <c r="BV39"/>
+      <c r="BW39"/>
+      <c r="BX39"/>
+      <c r="BY39"/>
+      <c r="BZ39"/>
+      <c r="CA39"/>
+      <c r="CB39"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
+    <row r="40">
+      <c r="A40" s="4"/>
       <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>0.2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40">
+        <v>0.24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40" s="42" t="n">
+        <v>84</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>0.24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>93</v>
+      </c>
+      <c r="K40">
+        <v>30</v>
+      </c>
+      <c r="L40" t="s">
+        <v>94</v>
+      </c>
+      <c r="M40">
+        <v>0.2</v>
+      </c>
+      <c r="N40" t="s">
         <v>37</v>
       </c>
-      <c r="C40">
-        <v>0.2</v>
-      </c>
-      <c r="D40" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40">
-        <v>0.24</v>
-      </c>
-      <c r="F40" t="s">
-        <v>72</v>
-      </c>
-      <c r="G40" s="10">
-        <v>0.84</v>
-      </c>
-      <c r="H40" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40">
-        <v>0.24</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40">
-        <v>30</v>
-      </c>
-      <c r="L40" t="s">
-        <v>28</v>
-      </c>
-      <c r="M40">
-        <v>0.2</v>
-      </c>
-      <c r="N40" t="s">
-        <v>18</v>
-      </c>
       <c r="O40">
         <v>30</v>
       </c>
@@ -2711,7 +5090,7 @@
         <v>30</v>
       </c>
       <c r="Q40" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R40">
         <v>4</v>
@@ -2719,56 +5098,117 @@
       <c r="S40">
         <v>3</v>
       </c>
+      <c r="T40"/>
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40"/>
+      <c r="Z40"/>
+      <c r="AA40"/>
+      <c r="AB40"/>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40"/>
+      <c r="AF40"/>
+      <c r="AG40"/>
+      <c r="AH40"/>
+      <c r="AI40"/>
+      <c r="AJ40"/>
+      <c r="AK40"/>
+      <c r="AL40"/>
+      <c r="AM40"/>
+      <c r="AN40"/>
+      <c r="AO40"/>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+      <c r="AR40"/>
+      <c r="AS40"/>
+      <c r="AT40"/>
+      <c r="AU40"/>
+      <c r="AV40"/>
+      <c r="AW40"/>
+      <c r="AX40"/>
+      <c r="AY40"/>
+      <c r="AZ40"/>
+      <c r="BA40"/>
+      <c r="BB40"/>
+      <c r="BC40"/>
+      <c r="BD40"/>
+      <c r="BE40"/>
+      <c r="BF40"/>
+      <c r="BG40"/>
+      <c r="BH40"/>
+      <c r="BI40"/>
+      <c r="BJ40"/>
+      <c r="BK40"/>
+      <c r="BL40"/>
+      <c r="BM40"/>
+      <c r="BN40"/>
+      <c r="BO40"/>
+      <c r="BP40"/>
+      <c r="BQ40"/>
+      <c r="BR40"/>
+      <c r="BS40"/>
+      <c r="BT40"/>
+      <c r="BU40"/>
+      <c r="BV40"/>
+      <c r="BW40"/>
+      <c r="BX40"/>
+      <c r="BY40"/>
+      <c r="BZ40"/>
+      <c r="CA40"/>
+      <c r="CB40"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
+    <row r="41">
+      <c r="A41" s="4"/>
       <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41">
+        <v>0.24</v>
+      </c>
+      <c r="F41" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41" s="42" t="n">
+        <v>82</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>0.24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>93</v>
+      </c>
+      <c r="K41">
+        <v>30</v>
+      </c>
+      <c r="L41" t="s">
+        <v>94</v>
+      </c>
+      <c r="M41">
+        <v>0.2</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41">
+        <v>30</v>
+      </c>
+      <c r="P41">
+        <v>30</v>
+      </c>
+      <c r="Q41" t="s">
         <v>38</v>
-      </c>
-      <c r="C41">
-        <v>0.2</v>
-      </c>
-      <c r="D41" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41">
-        <v>0.24</v>
-      </c>
-      <c r="F41" t="s">
-        <v>73</v>
-      </c>
-      <c r="G41" s="10">
-        <v>0.82</v>
-      </c>
-      <c r="H41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41">
-        <v>0.24</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41">
-        <v>30</v>
-      </c>
-      <c r="L41" t="s">
-        <v>28</v>
-      </c>
-      <c r="M41">
-        <v>0.2</v>
-      </c>
-      <c r="N41" t="s">
-        <v>18</v>
-      </c>
-      <c r="O41">
-        <v>30</v>
-      </c>
-      <c r="P41">
-        <v>30</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>33</v>
       </c>
       <c r="R41">
         <v>4</v>
@@ -2776,47 +5216,108 @@
       <c r="S41">
         <v>3</v>
       </c>
+      <c r="T41"/>
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41"/>
+      <c r="AF41"/>
+      <c r="AG41"/>
+      <c r="AH41"/>
+      <c r="AI41"/>
+      <c r="AJ41"/>
+      <c r="AK41"/>
+      <c r="AL41"/>
+      <c r="AM41"/>
+      <c r="AN41"/>
+      <c r="AO41"/>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41"/>
+      <c r="AS41"/>
+      <c r="AT41"/>
+      <c r="AU41"/>
+      <c r="AV41"/>
+      <c r="AW41"/>
+      <c r="AX41"/>
+      <c r="AY41"/>
+      <c r="AZ41"/>
+      <c r="BA41"/>
+      <c r="BB41"/>
+      <c r="BC41"/>
+      <c r="BD41"/>
+      <c r="BE41"/>
+      <c r="BF41"/>
+      <c r="BG41"/>
+      <c r="BH41"/>
+      <c r="BI41"/>
+      <c r="BJ41"/>
+      <c r="BK41"/>
+      <c r="BL41"/>
+      <c r="BM41"/>
+      <c r="BN41"/>
+      <c r="BO41"/>
+      <c r="BP41"/>
+      <c r="BQ41"/>
+      <c r="BR41"/>
+      <c r="BS41"/>
+      <c r="BT41"/>
+      <c r="BU41"/>
+      <c r="BV41"/>
+      <c r="BW41"/>
+      <c r="BX41"/>
+      <c r="BY41"/>
+      <c r="BZ41"/>
+      <c r="CA41"/>
+      <c r="CB41"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
+    <row r="42">
+      <c r="A42" s="4"/>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>0.2</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E42">
         <v>0.24</v>
       </c>
       <c r="F42" t="s">
-        <v>97</v>
-      </c>
-      <c r="G42" s="10">
-        <v>0.72</v>
+        <v>99</v>
+      </c>
+      <c r="G42" s="42" t="n">
+        <v>72</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I42">
         <v>0.24</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K42">
         <v>30</v>
       </c>
       <c r="L42" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M42">
         <v>0.2</v>
       </c>
       <c r="N42" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O42">
         <v>30</v>
@@ -2825,7 +5326,7 @@
         <v>30</v>
       </c>
       <c r="Q42" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R42">
         <v>4</v>
@@ -2833,47 +5334,108 @@
       <c r="S42">
         <v>3</v>
       </c>
+      <c r="T42"/>
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
+      <c r="AB42"/>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42"/>
+      <c r="AF42"/>
+      <c r="AG42"/>
+      <c r="AH42"/>
+      <c r="AI42"/>
+      <c r="AJ42"/>
+      <c r="AK42"/>
+      <c r="AL42"/>
+      <c r="AM42"/>
+      <c r="AN42"/>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
+      <c r="AS42"/>
+      <c r="AT42"/>
+      <c r="AU42"/>
+      <c r="AV42"/>
+      <c r="AW42"/>
+      <c r="AX42"/>
+      <c r="AY42"/>
+      <c r="AZ42"/>
+      <c r="BA42"/>
+      <c r="BB42"/>
+      <c r="BC42"/>
+      <c r="BD42"/>
+      <c r="BE42"/>
+      <c r="BF42"/>
+      <c r="BG42"/>
+      <c r="BH42"/>
+      <c r="BI42"/>
+      <c r="BJ42"/>
+      <c r="BK42"/>
+      <c r="BL42"/>
+      <c r="BM42"/>
+      <c r="BN42"/>
+      <c r="BO42"/>
+      <c r="BP42"/>
+      <c r="BQ42"/>
+      <c r="BR42"/>
+      <c r="BS42"/>
+      <c r="BT42"/>
+      <c r="BU42"/>
+      <c r="BV42"/>
+      <c r="BW42"/>
+      <c r="BX42"/>
+      <c r="BY42"/>
+      <c r="BZ42"/>
+      <c r="CA42"/>
+      <c r="CB42"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
+    <row r="43">
+      <c r="A43" s="4"/>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C43">
         <v>0.2</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E43">
         <v>0.24</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
-      </c>
-      <c r="G43" s="10">
-        <v>0.69</v>
+        <v>100</v>
+      </c>
+      <c r="G43" s="42" t="n">
+        <v>69</v>
       </c>
       <c r="H43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I43">
         <v>0.24</v>
       </c>
       <c r="J43" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K43">
         <v>30</v>
       </c>
       <c r="L43" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M43">
         <v>0.2</v>
       </c>
       <c r="N43" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O43">
         <v>30</v>
@@ -2882,7 +5444,7 @@
         <v>30</v>
       </c>
       <c r="Q43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R43">
         <v>4</v>
@@ -2890,47 +5452,108 @@
       <c r="S43">
         <v>3</v>
       </c>
+      <c r="T43"/>
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43"/>
+      <c r="Z43"/>
+      <c r="AA43"/>
+      <c r="AB43"/>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43"/>
+      <c r="AF43"/>
+      <c r="AG43"/>
+      <c r="AH43"/>
+      <c r="AI43"/>
+      <c r="AJ43"/>
+      <c r="AK43"/>
+      <c r="AL43"/>
+      <c r="AM43"/>
+      <c r="AN43"/>
+      <c r="AO43"/>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+      <c r="AR43"/>
+      <c r="AS43"/>
+      <c r="AT43"/>
+      <c r="AU43"/>
+      <c r="AV43"/>
+      <c r="AW43"/>
+      <c r="AX43"/>
+      <c r="AY43"/>
+      <c r="AZ43"/>
+      <c r="BA43"/>
+      <c r="BB43"/>
+      <c r="BC43"/>
+      <c r="BD43"/>
+      <c r="BE43"/>
+      <c r="BF43"/>
+      <c r="BG43"/>
+      <c r="BH43"/>
+      <c r="BI43"/>
+      <c r="BJ43"/>
+      <c r="BK43"/>
+      <c r="BL43"/>
+      <c r="BM43"/>
+      <c r="BN43"/>
+      <c r="BO43"/>
+      <c r="BP43"/>
+      <c r="BQ43"/>
+      <c r="BR43"/>
+      <c r="BS43"/>
+      <c r="BT43"/>
+      <c r="BU43"/>
+      <c r="BV43"/>
+      <c r="BW43"/>
+      <c r="BX43"/>
+      <c r="BY43"/>
+      <c r="BZ43"/>
+      <c r="CA43"/>
+      <c r="CB43"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
+    <row r="44">
+      <c r="A44" s="4"/>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>0.2</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E44">
         <v>0.24</v>
       </c>
       <c r="F44" t="s">
-        <v>99</v>
-      </c>
-      <c r="G44" s="10">
-        <v>0.88</v>
+        <v>101</v>
+      </c>
+      <c r="G44" s="42" t="n">
+        <v>88</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I44">
         <v>0.24</v>
       </c>
       <c r="J44" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K44">
         <v>30</v>
       </c>
       <c r="L44" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M44">
         <v>0.2</v>
       </c>
       <c r="N44" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O44">
         <v>30</v>
@@ -2939,7 +5562,7 @@
         <v>30</v>
       </c>
       <c r="Q44" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R44">
         <v>4</v>
@@ -2947,47 +5570,108 @@
       <c r="S44">
         <v>3</v>
       </c>
+      <c r="T44"/>
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+      <c r="AA44"/>
+      <c r="AB44"/>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44"/>
+      <c r="AF44"/>
+      <c r="AG44"/>
+      <c r="AH44"/>
+      <c r="AI44"/>
+      <c r="AJ44"/>
+      <c r="AK44"/>
+      <c r="AL44"/>
+      <c r="AM44"/>
+      <c r="AN44"/>
+      <c r="AO44"/>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44"/>
+      <c r="AS44"/>
+      <c r="AT44"/>
+      <c r="AU44"/>
+      <c r="AV44"/>
+      <c r="AW44"/>
+      <c r="AX44"/>
+      <c r="AY44"/>
+      <c r="AZ44"/>
+      <c r="BA44"/>
+      <c r="BB44"/>
+      <c r="BC44"/>
+      <c r="BD44"/>
+      <c r="BE44"/>
+      <c r="BF44"/>
+      <c r="BG44"/>
+      <c r="BH44"/>
+      <c r="BI44"/>
+      <c r="BJ44"/>
+      <c r="BK44"/>
+      <c r="BL44"/>
+      <c r="BM44"/>
+      <c r="BN44"/>
+      <c r="BO44"/>
+      <c r="BP44"/>
+      <c r="BQ44"/>
+      <c r="BR44"/>
+      <c r="BS44"/>
+      <c r="BT44"/>
+      <c r="BU44"/>
+      <c r="BV44"/>
+      <c r="BW44"/>
+      <c r="BX44"/>
+      <c r="BY44"/>
+      <c r="BZ44"/>
+      <c r="CA44"/>
+      <c r="CB44"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
+    <row r="45">
+      <c r="A45" s="4"/>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C45">
         <v>0.2</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E45">
         <v>0.24</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="10">
-        <v>0.81</v>
+        <v>102</v>
+      </c>
+      <c r="G45" s="42" t="n">
+        <v>81</v>
       </c>
       <c r="H45" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I45">
         <v>0.24</v>
       </c>
       <c r="J45" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K45">
         <v>30</v>
       </c>
       <c r="L45" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M45">
         <v>0.2</v>
       </c>
       <c r="N45" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O45">
         <v>30</v>
@@ -2996,7 +5680,7 @@
         <v>30</v>
       </c>
       <c r="Q45" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R45">
         <v>4</v>
@@ -3004,47 +5688,108 @@
       <c r="S45">
         <v>3</v>
       </c>
+      <c r="T45"/>
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45"/>
+      <c r="Z45"/>
+      <c r="AA45"/>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45"/>
+      <c r="AF45"/>
+      <c r="AG45"/>
+      <c r="AH45"/>
+      <c r="AI45"/>
+      <c r="AJ45"/>
+      <c r="AK45"/>
+      <c r="AL45"/>
+      <c r="AM45"/>
+      <c r="AN45"/>
+      <c r="AO45"/>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+      <c r="AR45"/>
+      <c r="AS45"/>
+      <c r="AT45"/>
+      <c r="AU45"/>
+      <c r="AV45"/>
+      <c r="AW45"/>
+      <c r="AX45"/>
+      <c r="AY45"/>
+      <c r="AZ45"/>
+      <c r="BA45"/>
+      <c r="BB45"/>
+      <c r="BC45"/>
+      <c r="BD45"/>
+      <c r="BE45"/>
+      <c r="BF45"/>
+      <c r="BG45"/>
+      <c r="BH45"/>
+      <c r="BI45"/>
+      <c r="BJ45"/>
+      <c r="BK45"/>
+      <c r="BL45"/>
+      <c r="BM45"/>
+      <c r="BN45"/>
+      <c r="BO45"/>
+      <c r="BP45"/>
+      <c r="BQ45"/>
+      <c r="BR45"/>
+      <c r="BS45"/>
+      <c r="BT45"/>
+      <c r="BU45"/>
+      <c r="BV45"/>
+      <c r="BW45"/>
+      <c r="BX45"/>
+      <c r="BY45"/>
+      <c r="BZ45"/>
+      <c r="CA45"/>
+      <c r="CB45"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
+    <row r="46">
+      <c r="A46" s="4"/>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>0.2</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E46">
         <v>0.24</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
-      </c>
-      <c r="G46" s="10">
-        <v>0.79</v>
+        <v>103</v>
+      </c>
+      <c r="G46" s="42" t="n">
+        <v>79</v>
       </c>
       <c r="H46" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I46">
         <v>0.24</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K46">
         <v>30</v>
       </c>
       <c r="L46" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M46">
         <v>0.2</v>
       </c>
       <c r="N46" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O46">
         <v>30</v>
@@ -3053,7 +5798,7 @@
         <v>30</v>
       </c>
       <c r="Q46" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R46">
         <v>4</v>
@@ -3061,47 +5806,108 @@
       <c r="S46">
         <v>3</v>
       </c>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
+      <c r="AJ46"/>
+      <c r="AK46"/>
+      <c r="AL46"/>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
+      <c r="AS46"/>
+      <c r="AT46"/>
+      <c r="AU46"/>
+      <c r="AV46"/>
+      <c r="AW46"/>
+      <c r="AX46"/>
+      <c r="AY46"/>
+      <c r="AZ46"/>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46"/>
+      <c r="BD46"/>
+      <c r="BE46"/>
+      <c r="BF46"/>
+      <c r="BG46"/>
+      <c r="BH46"/>
+      <c r="BI46"/>
+      <c r="BJ46"/>
+      <c r="BK46"/>
+      <c r="BL46"/>
+      <c r="BM46"/>
+      <c r="BN46"/>
+      <c r="BO46"/>
+      <c r="BP46"/>
+      <c r="BQ46"/>
+      <c r="BR46"/>
+      <c r="BS46"/>
+      <c r="BT46"/>
+      <c r="BU46"/>
+      <c r="BV46"/>
+      <c r="BW46"/>
+      <c r="BX46"/>
+      <c r="BY46"/>
+      <c r="BZ46"/>
+      <c r="CA46"/>
+      <c r="CB46"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
+    <row r="47">
+      <c r="A47" s="4"/>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C47">
         <v>0.2</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E47">
         <v>0.24</v>
       </c>
       <c r="F47" t="s">
-        <v>102</v>
-      </c>
-      <c r="G47" s="10">
-        <v>0.75</v>
+        <v>104</v>
+      </c>
+      <c r="G47" s="42" t="n">
+        <v>75</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I47">
         <v>0.24</v>
       </c>
       <c r="J47" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K47">
         <v>30</v>
       </c>
       <c r="L47" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M47">
         <v>0.2</v>
       </c>
       <c r="N47" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O47">
         <v>30</v>
@@ -3110,7 +5916,7 @@
         <v>30</v>
       </c>
       <c r="Q47" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R47">
         <v>4</v>
@@ -3118,47 +5924,108 @@
       <c r="S47">
         <v>3</v>
       </c>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+      <c r="AF47"/>
+      <c r="AG47"/>
+      <c r="AH47"/>
+      <c r="AI47"/>
+      <c r="AJ47"/>
+      <c r="AK47"/>
+      <c r="AL47"/>
+      <c r="AM47"/>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
+      <c r="AS47"/>
+      <c r="AT47"/>
+      <c r="AU47"/>
+      <c r="AV47"/>
+      <c r="AW47"/>
+      <c r="AX47"/>
+      <c r="AY47"/>
+      <c r="AZ47"/>
+      <c r="BA47"/>
+      <c r="BB47"/>
+      <c r="BC47"/>
+      <c r="BD47"/>
+      <c r="BE47"/>
+      <c r="BF47"/>
+      <c r="BG47"/>
+      <c r="BH47"/>
+      <c r="BI47"/>
+      <c r="BJ47"/>
+      <c r="BK47"/>
+      <c r="BL47"/>
+      <c r="BM47"/>
+      <c r="BN47"/>
+      <c r="BO47"/>
+      <c r="BP47"/>
+      <c r="BQ47"/>
+      <c r="BR47"/>
+      <c r="BS47"/>
+      <c r="BT47"/>
+      <c r="BU47"/>
+      <c r="BV47"/>
+      <c r="BW47"/>
+      <c r="BX47"/>
+      <c r="BY47"/>
+      <c r="BZ47"/>
+      <c r="CA47"/>
+      <c r="CB47"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A48" s="2"/>
+    <row r="48">
+      <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C48">
         <v>0.2</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E48">
         <v>0.24</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" s="10">
-        <v>0.8</v>
+        <v>105</v>
+      </c>
+      <c r="G48" s="42" t="n">
+        <v>80</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I48">
         <v>0.24</v>
       </c>
       <c r="J48" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K48">
         <v>30</v>
       </c>
       <c r="L48" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M48">
         <v>0.2</v>
       </c>
       <c r="N48" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O48">
         <v>30</v>
@@ -3167,7 +6034,7 @@
         <v>30</v>
       </c>
       <c r="Q48" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R48">
         <v>4</v>
@@ -3175,47 +6042,108 @@
       <c r="S48">
         <v>3</v>
       </c>
+      <c r="T48"/>
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="Y48"/>
+      <c r="Z48"/>
+      <c r="AA48"/>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48"/>
+      <c r="AF48"/>
+      <c r="AG48"/>
+      <c r="AH48"/>
+      <c r="AI48"/>
+      <c r="AJ48"/>
+      <c r="AK48"/>
+      <c r="AL48"/>
+      <c r="AM48"/>
+      <c r="AN48"/>
+      <c r="AO48"/>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48"/>
+      <c r="AS48"/>
+      <c r="AT48"/>
+      <c r="AU48"/>
+      <c r="AV48"/>
+      <c r="AW48"/>
+      <c r="AX48"/>
+      <c r="AY48"/>
+      <c r="AZ48"/>
+      <c r="BA48"/>
+      <c r="BB48"/>
+      <c r="BC48"/>
+      <c r="BD48"/>
+      <c r="BE48"/>
+      <c r="BF48"/>
+      <c r="BG48"/>
+      <c r="BH48"/>
+      <c r="BI48"/>
+      <c r="BJ48"/>
+      <c r="BK48"/>
+      <c r="BL48"/>
+      <c r="BM48"/>
+      <c r="BN48"/>
+      <c r="BO48"/>
+      <c r="BP48"/>
+      <c r="BQ48"/>
+      <c r="BR48"/>
+      <c r="BS48"/>
+      <c r="BT48"/>
+      <c r="BU48"/>
+      <c r="BV48"/>
+      <c r="BW48"/>
+      <c r="BX48"/>
+      <c r="BY48"/>
+      <c r="BZ48"/>
+      <c r="CA48"/>
+      <c r="CB48"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
+    <row r="49">
+      <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C49">
         <v>0.2</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E49">
         <v>0.24</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
-      </c>
-      <c r="G49" s="10">
-        <v>0.82</v>
+        <v>106</v>
+      </c>
+      <c r="G49" s="42" t="n">
+        <v>82</v>
       </c>
       <c r="H49" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I49">
         <v>0.24</v>
       </c>
       <c r="J49" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K49">
         <v>30</v>
       </c>
       <c r="L49" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M49">
         <v>0.2</v>
       </c>
       <c r="N49" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O49">
         <v>30</v>
@@ -3224,7 +6152,7 @@
         <v>30</v>
       </c>
       <c r="Q49" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R49">
         <v>4</v>
@@ -3232,47 +6160,108 @@
       <c r="S49">
         <v>3</v>
       </c>
+      <c r="T49"/>
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+      <c r="Y49"/>
+      <c r="Z49"/>
+      <c r="AA49"/>
+      <c r="AB49"/>
+      <c r="AC49"/>
+      <c r="AD49"/>
+      <c r="AE49"/>
+      <c r="AF49"/>
+      <c r="AG49"/>
+      <c r="AH49"/>
+      <c r="AI49"/>
+      <c r="AJ49"/>
+      <c r="AK49"/>
+      <c r="AL49"/>
+      <c r="AM49"/>
+      <c r="AN49"/>
+      <c r="AO49"/>
+      <c r="AP49"/>
+      <c r="AQ49"/>
+      <c r="AR49"/>
+      <c r="AS49"/>
+      <c r="AT49"/>
+      <c r="AU49"/>
+      <c r="AV49"/>
+      <c r="AW49"/>
+      <c r="AX49"/>
+      <c r="AY49"/>
+      <c r="AZ49"/>
+      <c r="BA49"/>
+      <c r="BB49"/>
+      <c r="BC49"/>
+      <c r="BD49"/>
+      <c r="BE49"/>
+      <c r="BF49"/>
+      <c r="BG49"/>
+      <c r="BH49"/>
+      <c r="BI49"/>
+      <c r="BJ49"/>
+      <c r="BK49"/>
+      <c r="BL49"/>
+      <c r="BM49"/>
+      <c r="BN49"/>
+      <c r="BO49"/>
+      <c r="BP49"/>
+      <c r="BQ49"/>
+      <c r="BR49"/>
+      <c r="BS49"/>
+      <c r="BT49"/>
+      <c r="BU49"/>
+      <c r="BV49"/>
+      <c r="BW49"/>
+      <c r="BX49"/>
+      <c r="BY49"/>
+      <c r="BZ49"/>
+      <c r="CA49"/>
+      <c r="CB49"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
+    <row r="50">
+      <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C50">
         <v>0.2</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E50">
         <v>0.24</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
-      </c>
-      <c r="G50" s="10">
-        <v>0.8</v>
+        <v>107</v>
+      </c>
+      <c r="G50" s="42" t="n">
+        <v>80</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I50">
         <v>0.24</v>
       </c>
       <c r="J50" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K50">
         <v>30</v>
       </c>
       <c r="L50" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M50">
         <v>0.2</v>
       </c>
       <c r="N50" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O50">
         <v>30</v>
@@ -3281,7 +6270,7 @@
         <v>30</v>
       </c>
       <c r="Q50" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R50">
         <v>4</v>
@@ -3289,47 +6278,108 @@
       <c r="S50">
         <v>3</v>
       </c>
+      <c r="T50"/>
+      <c r="U50"/>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+      <c r="Y50"/>
+      <c r="Z50"/>
+      <c r="AA50"/>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
+      <c r="AE50"/>
+      <c r="AF50"/>
+      <c r="AG50"/>
+      <c r="AH50"/>
+      <c r="AI50"/>
+      <c r="AJ50"/>
+      <c r="AK50"/>
+      <c r="AL50"/>
+      <c r="AM50"/>
+      <c r="AN50"/>
+      <c r="AO50"/>
+      <c r="AP50"/>
+      <c r="AQ50"/>
+      <c r="AR50"/>
+      <c r="AS50"/>
+      <c r="AT50"/>
+      <c r="AU50"/>
+      <c r="AV50"/>
+      <c r="AW50"/>
+      <c r="AX50"/>
+      <c r="AY50"/>
+      <c r="AZ50"/>
+      <c r="BA50"/>
+      <c r="BB50"/>
+      <c r="BC50"/>
+      <c r="BD50"/>
+      <c r="BE50"/>
+      <c r="BF50"/>
+      <c r="BG50"/>
+      <c r="BH50"/>
+      <c r="BI50"/>
+      <c r="BJ50"/>
+      <c r="BK50"/>
+      <c r="BL50"/>
+      <c r="BM50"/>
+      <c r="BN50"/>
+      <c r="BO50"/>
+      <c r="BP50"/>
+      <c r="BQ50"/>
+      <c r="BR50"/>
+      <c r="BS50"/>
+      <c r="BT50"/>
+      <c r="BU50"/>
+      <c r="BV50"/>
+      <c r="BW50"/>
+      <c r="BX50"/>
+      <c r="BY50"/>
+      <c r="BZ50"/>
+      <c r="CA50"/>
+      <c r="CB50"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
+    <row r="51">
+      <c r="A51" s="4"/>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C51">
         <v>0.2</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E51">
         <v>0.24</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0.75</v>
+        <v>108</v>
+      </c>
+      <c r="G51" s="42" t="n">
+        <v>75</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I51">
         <v>0.24</v>
       </c>
       <c r="J51" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K51">
         <v>30</v>
       </c>
       <c r="L51" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M51">
         <v>0.2</v>
       </c>
       <c r="N51" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O51">
         <v>30</v>
@@ -3338,7 +6388,7 @@
         <v>30</v>
       </c>
       <c r="Q51" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R51">
         <v>4</v>
@@ -3346,47 +6396,108 @@
       <c r="S51">
         <v>3</v>
       </c>
+      <c r="T51"/>
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+      <c r="AB51"/>
+      <c r="AC51"/>
+      <c r="AD51"/>
+      <c r="AE51"/>
+      <c r="AF51"/>
+      <c r="AG51"/>
+      <c r="AH51"/>
+      <c r="AI51"/>
+      <c r="AJ51"/>
+      <c r="AK51"/>
+      <c r="AL51"/>
+      <c r="AM51"/>
+      <c r="AN51"/>
+      <c r="AO51"/>
+      <c r="AP51"/>
+      <c r="AQ51"/>
+      <c r="AR51"/>
+      <c r="AS51"/>
+      <c r="AT51"/>
+      <c r="AU51"/>
+      <c r="AV51"/>
+      <c r="AW51"/>
+      <c r="AX51"/>
+      <c r="AY51"/>
+      <c r="AZ51"/>
+      <c r="BA51"/>
+      <c r="BB51"/>
+      <c r="BC51"/>
+      <c r="BD51"/>
+      <c r="BE51"/>
+      <c r="BF51"/>
+      <c r="BG51"/>
+      <c r="BH51"/>
+      <c r="BI51"/>
+      <c r="BJ51"/>
+      <c r="BK51"/>
+      <c r="BL51"/>
+      <c r="BM51"/>
+      <c r="BN51"/>
+      <c r="BO51"/>
+      <c r="BP51"/>
+      <c r="BQ51"/>
+      <c r="BR51"/>
+      <c r="BS51"/>
+      <c r="BT51"/>
+      <c r="BU51"/>
+      <c r="BV51"/>
+      <c r="BW51"/>
+      <c r="BX51"/>
+      <c r="BY51"/>
+      <c r="BZ51"/>
+      <c r="CA51"/>
+      <c r="CB51"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
+    <row r="52">
+      <c r="A52" s="4"/>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>0.2</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E52">
         <v>0.24</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
-      </c>
-      <c r="G52" s="10">
-        <v>0.87</v>
+        <v>109</v>
+      </c>
+      <c r="G52" s="42" t="n">
+        <v>87</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I52">
         <v>0.24</v>
       </c>
       <c r="J52" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K52">
         <v>30</v>
       </c>
       <c r="L52" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M52">
         <v>0.2</v>
       </c>
       <c r="N52" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O52">
         <v>30</v>
@@ -3395,7 +6506,7 @@
         <v>30</v>
       </c>
       <c r="Q52" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R52">
         <v>4</v>
@@ -3403,47 +6514,108 @@
       <c r="S52">
         <v>3</v>
       </c>
+      <c r="T52"/>
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+      <c r="Y52"/>
+      <c r="Z52"/>
+      <c r="AA52"/>
+      <c r="AB52"/>
+      <c r="AC52"/>
+      <c r="AD52"/>
+      <c r="AE52"/>
+      <c r="AF52"/>
+      <c r="AG52"/>
+      <c r="AH52"/>
+      <c r="AI52"/>
+      <c r="AJ52"/>
+      <c r="AK52"/>
+      <c r="AL52"/>
+      <c r="AM52"/>
+      <c r="AN52"/>
+      <c r="AO52"/>
+      <c r="AP52"/>
+      <c r="AQ52"/>
+      <c r="AR52"/>
+      <c r="AS52"/>
+      <c r="AT52"/>
+      <c r="AU52"/>
+      <c r="AV52"/>
+      <c r="AW52"/>
+      <c r="AX52"/>
+      <c r="AY52"/>
+      <c r="AZ52"/>
+      <c r="BA52"/>
+      <c r="BB52"/>
+      <c r="BC52"/>
+      <c r="BD52"/>
+      <c r="BE52"/>
+      <c r="BF52"/>
+      <c r="BG52"/>
+      <c r="BH52"/>
+      <c r="BI52"/>
+      <c r="BJ52"/>
+      <c r="BK52"/>
+      <c r="BL52"/>
+      <c r="BM52"/>
+      <c r="BN52"/>
+      <c r="BO52"/>
+      <c r="BP52"/>
+      <c r="BQ52"/>
+      <c r="BR52"/>
+      <c r="BS52"/>
+      <c r="BT52"/>
+      <c r="BU52"/>
+      <c r="BV52"/>
+      <c r="BW52"/>
+      <c r="BX52"/>
+      <c r="BY52"/>
+      <c r="BZ52"/>
+      <c r="CA52"/>
+      <c r="CB52"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
+    <row r="53">
+      <c r="A53" s="4"/>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>0.2</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E53">
         <v>0.24</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
-      </c>
-      <c r="G53" s="10">
-        <v>0.77</v>
+        <v>110</v>
+      </c>
+      <c r="G53" s="42" t="n">
+        <v>77</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I53">
         <v>0.24</v>
       </c>
       <c r="J53" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K53">
         <v>30</v>
       </c>
       <c r="L53" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M53">
         <v>0.2</v>
       </c>
       <c r="N53" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O53">
         <v>30</v>
@@ -3452,7 +6624,7 @@
         <v>30</v>
       </c>
       <c r="Q53" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R53">
         <v>4</v>
@@ -3460,47 +6632,108 @@
       <c r="S53">
         <v>3</v>
       </c>
+      <c r="T53"/>
+      <c r="U53"/>
+      <c r="V53"/>
+      <c r="W53"/>
+      <c r="X53"/>
+      <c r="Y53"/>
+      <c r="Z53"/>
+      <c r="AA53"/>
+      <c r="AB53"/>
+      <c r="AC53"/>
+      <c r="AD53"/>
+      <c r="AE53"/>
+      <c r="AF53"/>
+      <c r="AG53"/>
+      <c r="AH53"/>
+      <c r="AI53"/>
+      <c r="AJ53"/>
+      <c r="AK53"/>
+      <c r="AL53"/>
+      <c r="AM53"/>
+      <c r="AN53"/>
+      <c r="AO53"/>
+      <c r="AP53"/>
+      <c r="AQ53"/>
+      <c r="AR53"/>
+      <c r="AS53"/>
+      <c r="AT53"/>
+      <c r="AU53"/>
+      <c r="AV53"/>
+      <c r="AW53"/>
+      <c r="AX53"/>
+      <c r="AY53"/>
+      <c r="AZ53"/>
+      <c r="BA53"/>
+      <c r="BB53"/>
+      <c r="BC53"/>
+      <c r="BD53"/>
+      <c r="BE53"/>
+      <c r="BF53"/>
+      <c r="BG53"/>
+      <c r="BH53"/>
+      <c r="BI53"/>
+      <c r="BJ53"/>
+      <c r="BK53"/>
+      <c r="BL53"/>
+      <c r="BM53"/>
+      <c r="BN53"/>
+      <c r="BO53"/>
+      <c r="BP53"/>
+      <c r="BQ53"/>
+      <c r="BR53"/>
+      <c r="BS53"/>
+      <c r="BT53"/>
+      <c r="BU53"/>
+      <c r="BV53"/>
+      <c r="BW53"/>
+      <c r="BX53"/>
+      <c r="BY53"/>
+      <c r="BZ53"/>
+      <c r="CA53"/>
+      <c r="CB53"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
+    <row r="54">
+      <c r="A54" s="4"/>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C54">
         <v>0.2</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E54">
         <v>0.24</v>
       </c>
       <c r="F54" t="s">
-        <v>109</v>
-      </c>
-      <c r="G54" s="10">
-        <v>0.88</v>
+        <v>111</v>
+      </c>
+      <c r="G54" s="42" t="n">
+        <v>88</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I54">
         <v>0.24</v>
       </c>
       <c r="J54" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K54">
         <v>30</v>
       </c>
       <c r="L54" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M54">
         <v>0.2</v>
       </c>
       <c r="N54" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O54">
         <v>30</v>
@@ -3509,7 +6742,7 @@
         <v>30</v>
       </c>
       <c r="Q54" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R54">
         <v>4</v>
@@ -3517,47 +6750,108 @@
       <c r="S54">
         <v>3</v>
       </c>
+      <c r="T54"/>
+      <c r="U54"/>
+      <c r="V54"/>
+      <c r="W54"/>
+      <c r="X54"/>
+      <c r="Y54"/>
+      <c r="Z54"/>
+      <c r="AA54"/>
+      <c r="AB54"/>
+      <c r="AC54"/>
+      <c r="AD54"/>
+      <c r="AE54"/>
+      <c r="AF54"/>
+      <c r="AG54"/>
+      <c r="AH54"/>
+      <c r="AI54"/>
+      <c r="AJ54"/>
+      <c r="AK54"/>
+      <c r="AL54"/>
+      <c r="AM54"/>
+      <c r="AN54"/>
+      <c r="AO54"/>
+      <c r="AP54"/>
+      <c r="AQ54"/>
+      <c r="AR54"/>
+      <c r="AS54"/>
+      <c r="AT54"/>
+      <c r="AU54"/>
+      <c r="AV54"/>
+      <c r="AW54"/>
+      <c r="AX54"/>
+      <c r="AY54"/>
+      <c r="AZ54"/>
+      <c r="BA54"/>
+      <c r="BB54"/>
+      <c r="BC54"/>
+      <c r="BD54"/>
+      <c r="BE54"/>
+      <c r="BF54"/>
+      <c r="BG54"/>
+      <c r="BH54"/>
+      <c r="BI54"/>
+      <c r="BJ54"/>
+      <c r="BK54"/>
+      <c r="BL54"/>
+      <c r="BM54"/>
+      <c r="BN54"/>
+      <c r="BO54"/>
+      <c r="BP54"/>
+      <c r="BQ54"/>
+      <c r="BR54"/>
+      <c r="BS54"/>
+      <c r="BT54"/>
+      <c r="BU54"/>
+      <c r="BV54"/>
+      <c r="BW54"/>
+      <c r="BX54"/>
+      <c r="BY54"/>
+      <c r="BZ54"/>
+      <c r="CA54"/>
+      <c r="CB54"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
+    <row r="55">
+      <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C55">
         <v>0.2</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E55">
         <v>0.24</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
-      </c>
-      <c r="G55" s="10">
-        <v>0.91</v>
+        <v>112</v>
+      </c>
+      <c r="G55" s="42" t="n">
+        <v>91</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I55">
         <v>0.24</v>
       </c>
       <c r="J55" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K55">
         <v>30</v>
       </c>
       <c r="L55" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M55">
         <v>0.2</v>
       </c>
       <c r="N55" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O55">
         <v>30</v>
@@ -3566,7 +6860,7 @@
         <v>30</v>
       </c>
       <c r="Q55" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R55">
         <v>4</v>
@@ -3574,47 +6868,108 @@
       <c r="S55">
         <v>3</v>
       </c>
+      <c r="T55"/>
+      <c r="U55"/>
+      <c r="V55"/>
+      <c r="W55"/>
+      <c r="X55"/>
+      <c r="Y55"/>
+      <c r="Z55"/>
+      <c r="AA55"/>
+      <c r="AB55"/>
+      <c r="AC55"/>
+      <c r="AD55"/>
+      <c r="AE55"/>
+      <c r="AF55"/>
+      <c r="AG55"/>
+      <c r="AH55"/>
+      <c r="AI55"/>
+      <c r="AJ55"/>
+      <c r="AK55"/>
+      <c r="AL55"/>
+      <c r="AM55"/>
+      <c r="AN55"/>
+      <c r="AO55"/>
+      <c r="AP55"/>
+      <c r="AQ55"/>
+      <c r="AR55"/>
+      <c r="AS55"/>
+      <c r="AT55"/>
+      <c r="AU55"/>
+      <c r="AV55"/>
+      <c r="AW55"/>
+      <c r="AX55"/>
+      <c r="AY55"/>
+      <c r="AZ55"/>
+      <c r="BA55"/>
+      <c r="BB55"/>
+      <c r="BC55"/>
+      <c r="BD55"/>
+      <c r="BE55"/>
+      <c r="BF55"/>
+      <c r="BG55"/>
+      <c r="BH55"/>
+      <c r="BI55"/>
+      <c r="BJ55"/>
+      <c r="BK55"/>
+      <c r="BL55"/>
+      <c r="BM55"/>
+      <c r="BN55"/>
+      <c r="BO55"/>
+      <c r="BP55"/>
+      <c r="BQ55"/>
+      <c r="BR55"/>
+      <c r="BS55"/>
+      <c r="BT55"/>
+      <c r="BU55"/>
+      <c r="BV55"/>
+      <c r="BW55"/>
+      <c r="BX55"/>
+      <c r="BY55"/>
+      <c r="BZ55"/>
+      <c r="CA55"/>
+      <c r="CB55"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A56" s="2"/>
+    <row r="56">
+      <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>0.2</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E56">
         <v>0.24</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
-      </c>
-      <c r="G56" s="10">
-        <v>0.85</v>
+        <v>113</v>
+      </c>
+      <c r="G56" s="42" t="n">
+        <v>85</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I56">
         <v>0.24</v>
       </c>
       <c r="J56" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K56">
         <v>30</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M56">
         <v>0.2</v>
       </c>
       <c r="N56" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O56">
         <v>30</v>
@@ -3623,7 +6978,7 @@
         <v>30</v>
       </c>
       <c r="Q56" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R56">
         <v>4</v>
@@ -3631,47 +6986,108 @@
       <c r="S56">
         <v>3</v>
       </c>
+      <c r="T56"/>
+      <c r="U56"/>
+      <c r="V56"/>
+      <c r="W56"/>
+      <c r="X56"/>
+      <c r="Y56"/>
+      <c r="Z56"/>
+      <c r="AA56"/>
+      <c r="AB56"/>
+      <c r="AC56"/>
+      <c r="AD56"/>
+      <c r="AE56"/>
+      <c r="AF56"/>
+      <c r="AG56"/>
+      <c r="AH56"/>
+      <c r="AI56"/>
+      <c r="AJ56"/>
+      <c r="AK56"/>
+      <c r="AL56"/>
+      <c r="AM56"/>
+      <c r="AN56"/>
+      <c r="AO56"/>
+      <c r="AP56"/>
+      <c r="AQ56"/>
+      <c r="AR56"/>
+      <c r="AS56"/>
+      <c r="AT56"/>
+      <c r="AU56"/>
+      <c r="AV56"/>
+      <c r="AW56"/>
+      <c r="AX56"/>
+      <c r="AY56"/>
+      <c r="AZ56"/>
+      <c r="BA56"/>
+      <c r="BB56"/>
+      <c r="BC56"/>
+      <c r="BD56"/>
+      <c r="BE56"/>
+      <c r="BF56"/>
+      <c r="BG56"/>
+      <c r="BH56"/>
+      <c r="BI56"/>
+      <c r="BJ56"/>
+      <c r="BK56"/>
+      <c r="BL56"/>
+      <c r="BM56"/>
+      <c r="BN56"/>
+      <c r="BO56"/>
+      <c r="BP56"/>
+      <c r="BQ56"/>
+      <c r="BR56"/>
+      <c r="BS56"/>
+      <c r="BT56"/>
+      <c r="BU56"/>
+      <c r="BV56"/>
+      <c r="BW56"/>
+      <c r="BX56"/>
+      <c r="BY56"/>
+      <c r="BZ56"/>
+      <c r="CA56"/>
+      <c r="CB56"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
+    <row r="57">
+      <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C57">
         <v>0.2</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E57">
         <v>0.24</v>
       </c>
       <c r="F57" t="s">
-        <v>112</v>
-      </c>
-      <c r="G57" s="10">
-        <v>0.82</v>
+        <v>114</v>
+      </c>
+      <c r="G57" s="42" t="n">
+        <v>82</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I57">
         <v>0.24</v>
       </c>
       <c r="J57" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K57">
         <v>30</v>
       </c>
       <c r="L57" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M57">
         <v>0.2</v>
       </c>
       <c r="N57" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O57">
         <v>30</v>
@@ -3680,7 +7096,7 @@
         <v>30</v>
       </c>
       <c r="Q57" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R57">
         <v>4</v>
@@ -3688,47 +7104,108 @@
       <c r="S57">
         <v>3</v>
       </c>
+      <c r="T57"/>
+      <c r="U57"/>
+      <c r="V57"/>
+      <c r="W57"/>
+      <c r="X57"/>
+      <c r="Y57"/>
+      <c r="Z57"/>
+      <c r="AA57"/>
+      <c r="AB57"/>
+      <c r="AC57"/>
+      <c r="AD57"/>
+      <c r="AE57"/>
+      <c r="AF57"/>
+      <c r="AG57"/>
+      <c r="AH57"/>
+      <c r="AI57"/>
+      <c r="AJ57"/>
+      <c r="AK57"/>
+      <c r="AL57"/>
+      <c r="AM57"/>
+      <c r="AN57"/>
+      <c r="AO57"/>
+      <c r="AP57"/>
+      <c r="AQ57"/>
+      <c r="AR57"/>
+      <c r="AS57"/>
+      <c r="AT57"/>
+      <c r="AU57"/>
+      <c r="AV57"/>
+      <c r="AW57"/>
+      <c r="AX57"/>
+      <c r="AY57"/>
+      <c r="AZ57"/>
+      <c r="BA57"/>
+      <c r="BB57"/>
+      <c r="BC57"/>
+      <c r="BD57"/>
+      <c r="BE57"/>
+      <c r="BF57"/>
+      <c r="BG57"/>
+      <c r="BH57"/>
+      <c r="BI57"/>
+      <c r="BJ57"/>
+      <c r="BK57"/>
+      <c r="BL57"/>
+      <c r="BM57"/>
+      <c r="BN57"/>
+      <c r="BO57"/>
+      <c r="BP57"/>
+      <c r="BQ57"/>
+      <c r="BR57"/>
+      <c r="BS57"/>
+      <c r="BT57"/>
+      <c r="BU57"/>
+      <c r="BV57"/>
+      <c r="BW57"/>
+      <c r="BX57"/>
+      <c r="BY57"/>
+      <c r="BZ57"/>
+      <c r="CA57"/>
+      <c r="CB57"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A58" s="2"/>
+    <row r="58">
+      <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C58">
         <v>0.2</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E58">
         <v>0.24</v>
       </c>
       <c r="F58" t="s">
-        <v>113</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0.85</v>
+        <v>115</v>
+      </c>
+      <c r="G58" s="42" t="n">
+        <v>85</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I58">
         <v>0.24</v>
       </c>
       <c r="J58" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K58">
         <v>30</v>
       </c>
       <c r="L58" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M58">
         <v>0.2</v>
       </c>
       <c r="N58" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O58">
         <v>30</v>
@@ -3737,7 +7214,7 @@
         <v>30</v>
       </c>
       <c r="Q58" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R58">
         <v>4</v>
@@ -3745,47 +7222,108 @@
       <c r="S58">
         <v>3</v>
       </c>
+      <c r="T58"/>
+      <c r="U58"/>
+      <c r="V58"/>
+      <c r="W58"/>
+      <c r="X58"/>
+      <c r="Y58"/>
+      <c r="Z58"/>
+      <c r="AA58"/>
+      <c r="AB58"/>
+      <c r="AC58"/>
+      <c r="AD58"/>
+      <c r="AE58"/>
+      <c r="AF58"/>
+      <c r="AG58"/>
+      <c r="AH58"/>
+      <c r="AI58"/>
+      <c r="AJ58"/>
+      <c r="AK58"/>
+      <c r="AL58"/>
+      <c r="AM58"/>
+      <c r="AN58"/>
+      <c r="AO58"/>
+      <c r="AP58"/>
+      <c r="AQ58"/>
+      <c r="AR58"/>
+      <c r="AS58"/>
+      <c r="AT58"/>
+      <c r="AU58"/>
+      <c r="AV58"/>
+      <c r="AW58"/>
+      <c r="AX58"/>
+      <c r="AY58"/>
+      <c r="AZ58"/>
+      <c r="BA58"/>
+      <c r="BB58"/>
+      <c r="BC58"/>
+      <c r="BD58"/>
+      <c r="BE58"/>
+      <c r="BF58"/>
+      <c r="BG58"/>
+      <c r="BH58"/>
+      <c r="BI58"/>
+      <c r="BJ58"/>
+      <c r="BK58"/>
+      <c r="BL58"/>
+      <c r="BM58"/>
+      <c r="BN58"/>
+      <c r="BO58"/>
+      <c r="BP58"/>
+      <c r="BQ58"/>
+      <c r="BR58"/>
+      <c r="BS58"/>
+      <c r="BT58"/>
+      <c r="BU58"/>
+      <c r="BV58"/>
+      <c r="BW58"/>
+      <c r="BX58"/>
+      <c r="BY58"/>
+      <c r="BZ58"/>
+      <c r="CA58"/>
+      <c r="CB58"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A59" s="2"/>
+    <row r="59">
+      <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C59">
         <v>0.2</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E59">
         <v>0.24</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
-      </c>
-      <c r="G59" s="10">
-        <v>0.83</v>
+        <v>116</v>
+      </c>
+      <c r="G59" s="42" t="n">
+        <v>83</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I59">
         <v>0.24</v>
       </c>
       <c r="J59" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K59">
         <v>30</v>
       </c>
       <c r="L59" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M59">
         <v>0.2</v>
       </c>
       <c r="N59" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O59">
         <v>30</v>
@@ -3794,7 +7332,7 @@
         <v>30</v>
       </c>
       <c r="Q59" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R59">
         <v>4</v>
@@ -3802,47 +7340,108 @@
       <c r="S59">
         <v>3</v>
       </c>
+      <c r="T59"/>
+      <c r="U59"/>
+      <c r="V59"/>
+      <c r="W59"/>
+      <c r="X59"/>
+      <c r="Y59"/>
+      <c r="Z59"/>
+      <c r="AA59"/>
+      <c r="AB59"/>
+      <c r="AC59"/>
+      <c r="AD59"/>
+      <c r="AE59"/>
+      <c r="AF59"/>
+      <c r="AG59"/>
+      <c r="AH59"/>
+      <c r="AI59"/>
+      <c r="AJ59"/>
+      <c r="AK59"/>
+      <c r="AL59"/>
+      <c r="AM59"/>
+      <c r="AN59"/>
+      <c r="AO59"/>
+      <c r="AP59"/>
+      <c r="AQ59"/>
+      <c r="AR59"/>
+      <c r="AS59"/>
+      <c r="AT59"/>
+      <c r="AU59"/>
+      <c r="AV59"/>
+      <c r="AW59"/>
+      <c r="AX59"/>
+      <c r="AY59"/>
+      <c r="AZ59"/>
+      <c r="BA59"/>
+      <c r="BB59"/>
+      <c r="BC59"/>
+      <c r="BD59"/>
+      <c r="BE59"/>
+      <c r="BF59"/>
+      <c r="BG59"/>
+      <c r="BH59"/>
+      <c r="BI59"/>
+      <c r="BJ59"/>
+      <c r="BK59"/>
+      <c r="BL59"/>
+      <c r="BM59"/>
+      <c r="BN59"/>
+      <c r="BO59"/>
+      <c r="BP59"/>
+      <c r="BQ59"/>
+      <c r="BR59"/>
+      <c r="BS59"/>
+      <c r="BT59"/>
+      <c r="BU59"/>
+      <c r="BV59"/>
+      <c r="BW59"/>
+      <c r="BX59"/>
+      <c r="BY59"/>
+      <c r="BZ59"/>
+      <c r="CA59"/>
+      <c r="CB59"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A60" s="2"/>
+    <row r="60">
+      <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C60">
         <v>0.2</v>
       </c>
       <c r="D60" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E60">
         <v>0.24</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0.89</v>
+        <v>117</v>
+      </c>
+      <c r="G60" s="42" t="n">
+        <v>89</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I60">
         <v>0.24</v>
       </c>
       <c r="J60" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K60">
         <v>30</v>
       </c>
       <c r="L60" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M60">
         <v>0.2</v>
       </c>
       <c r="N60" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O60">
         <v>30</v>
@@ -3851,7 +7450,7 @@
         <v>30</v>
       </c>
       <c r="Q60" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R60">
         <v>4</v>
@@ -3859,47 +7458,108 @@
       <c r="S60">
         <v>3</v>
       </c>
+      <c r="T60"/>
+      <c r="U60"/>
+      <c r="V60"/>
+      <c r="W60"/>
+      <c r="X60"/>
+      <c r="Y60"/>
+      <c r="Z60"/>
+      <c r="AA60"/>
+      <c r="AB60"/>
+      <c r="AC60"/>
+      <c r="AD60"/>
+      <c r="AE60"/>
+      <c r="AF60"/>
+      <c r="AG60"/>
+      <c r="AH60"/>
+      <c r="AI60"/>
+      <c r="AJ60"/>
+      <c r="AK60"/>
+      <c r="AL60"/>
+      <c r="AM60"/>
+      <c r="AN60"/>
+      <c r="AO60"/>
+      <c r="AP60"/>
+      <c r="AQ60"/>
+      <c r="AR60"/>
+      <c r="AS60"/>
+      <c r="AT60"/>
+      <c r="AU60"/>
+      <c r="AV60"/>
+      <c r="AW60"/>
+      <c r="AX60"/>
+      <c r="AY60"/>
+      <c r="AZ60"/>
+      <c r="BA60"/>
+      <c r="BB60"/>
+      <c r="BC60"/>
+      <c r="BD60"/>
+      <c r="BE60"/>
+      <c r="BF60"/>
+      <c r="BG60"/>
+      <c r="BH60"/>
+      <c r="BI60"/>
+      <c r="BJ60"/>
+      <c r="BK60"/>
+      <c r="BL60"/>
+      <c r="BM60"/>
+      <c r="BN60"/>
+      <c r="BO60"/>
+      <c r="BP60"/>
+      <c r="BQ60"/>
+      <c r="BR60"/>
+      <c r="BS60"/>
+      <c r="BT60"/>
+      <c r="BU60"/>
+      <c r="BV60"/>
+      <c r="BW60"/>
+      <c r="BX60"/>
+      <c r="BY60"/>
+      <c r="BZ60"/>
+      <c r="CA60"/>
+      <c r="CB60"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A61" s="2"/>
+    <row r="61">
+      <c r="A61" s="4"/>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C61">
         <v>0.2</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E61">
         <v>0.24</v>
       </c>
       <c r="F61" t="s">
-        <v>116</v>
-      </c>
-      <c r="G61" s="10">
-        <v>0.81</v>
+        <v>118</v>
+      </c>
+      <c r="G61" s="42" t="n">
+        <v>81</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I61">
         <v>0.24</v>
       </c>
       <c r="J61" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K61">
         <v>30</v>
       </c>
       <c r="L61" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M61">
         <v>0.2</v>
       </c>
       <c r="N61" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O61">
         <v>30</v>
@@ -3908,7 +7568,7 @@
         <v>30</v>
       </c>
       <c r="Q61" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R61">
         <v>4</v>
@@ -3916,47 +7576,108 @@
       <c r="S61">
         <v>3</v>
       </c>
+      <c r="T61"/>
+      <c r="U61"/>
+      <c r="V61"/>
+      <c r="W61"/>
+      <c r="X61"/>
+      <c r="Y61"/>
+      <c r="Z61"/>
+      <c r="AA61"/>
+      <c r="AB61"/>
+      <c r="AC61"/>
+      <c r="AD61"/>
+      <c r="AE61"/>
+      <c r="AF61"/>
+      <c r="AG61"/>
+      <c r="AH61"/>
+      <c r="AI61"/>
+      <c r="AJ61"/>
+      <c r="AK61"/>
+      <c r="AL61"/>
+      <c r="AM61"/>
+      <c r="AN61"/>
+      <c r="AO61"/>
+      <c r="AP61"/>
+      <c r="AQ61"/>
+      <c r="AR61"/>
+      <c r="AS61"/>
+      <c r="AT61"/>
+      <c r="AU61"/>
+      <c r="AV61"/>
+      <c r="AW61"/>
+      <c r="AX61"/>
+      <c r="AY61"/>
+      <c r="AZ61"/>
+      <c r="BA61"/>
+      <c r="BB61"/>
+      <c r="BC61"/>
+      <c r="BD61"/>
+      <c r="BE61"/>
+      <c r="BF61"/>
+      <c r="BG61"/>
+      <c r="BH61"/>
+      <c r="BI61"/>
+      <c r="BJ61"/>
+      <c r="BK61"/>
+      <c r="BL61"/>
+      <c r="BM61"/>
+      <c r="BN61"/>
+      <c r="BO61"/>
+      <c r="BP61"/>
+      <c r="BQ61"/>
+      <c r="BR61"/>
+      <c r="BS61"/>
+      <c r="BT61"/>
+      <c r="BU61"/>
+      <c r="BV61"/>
+      <c r="BW61"/>
+      <c r="BX61"/>
+      <c r="BY61"/>
+      <c r="BZ61"/>
+      <c r="CA61"/>
+      <c r="CB61"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A62" s="2"/>
+    <row r="62">
+      <c r="A62" s="4"/>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>0.2</v>
       </c>
       <c r="D62" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E62">
         <v>0.24</v>
       </c>
       <c r="F62" t="s">
-        <v>117</v>
-      </c>
-      <c r="G62" s="10">
-        <v>0.82</v>
+        <v>119</v>
+      </c>
+      <c r="G62" s="42" t="n">
+        <v>82</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I62">
         <v>0.24</v>
       </c>
       <c r="J62" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K62">
         <v>30</v>
       </c>
       <c r="L62" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M62">
         <v>0.2</v>
       </c>
       <c r="N62" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O62">
         <v>30</v>
@@ -3965,7 +7686,7 @@
         <v>30</v>
       </c>
       <c r="Q62" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R62">
         <v>4</v>
@@ -3973,47 +7694,108 @@
       <c r="S62">
         <v>3</v>
       </c>
+      <c r="T62"/>
+      <c r="U62"/>
+      <c r="V62"/>
+      <c r="W62"/>
+      <c r="X62"/>
+      <c r="Y62"/>
+      <c r="Z62"/>
+      <c r="AA62"/>
+      <c r="AB62"/>
+      <c r="AC62"/>
+      <c r="AD62"/>
+      <c r="AE62"/>
+      <c r="AF62"/>
+      <c r="AG62"/>
+      <c r="AH62"/>
+      <c r="AI62"/>
+      <c r="AJ62"/>
+      <c r="AK62"/>
+      <c r="AL62"/>
+      <c r="AM62"/>
+      <c r="AN62"/>
+      <c r="AO62"/>
+      <c r="AP62"/>
+      <c r="AQ62"/>
+      <c r="AR62"/>
+      <c r="AS62"/>
+      <c r="AT62"/>
+      <c r="AU62"/>
+      <c r="AV62"/>
+      <c r="AW62"/>
+      <c r="AX62"/>
+      <c r="AY62"/>
+      <c r="AZ62"/>
+      <c r="BA62"/>
+      <c r="BB62"/>
+      <c r="BC62"/>
+      <c r="BD62"/>
+      <c r="BE62"/>
+      <c r="BF62"/>
+      <c r="BG62"/>
+      <c r="BH62"/>
+      <c r="BI62"/>
+      <c r="BJ62"/>
+      <c r="BK62"/>
+      <c r="BL62"/>
+      <c r="BM62"/>
+      <c r="BN62"/>
+      <c r="BO62"/>
+      <c r="BP62"/>
+      <c r="BQ62"/>
+      <c r="BR62"/>
+      <c r="BS62"/>
+      <c r="BT62"/>
+      <c r="BU62"/>
+      <c r="BV62"/>
+      <c r="BW62"/>
+      <c r="BX62"/>
+      <c r="BY62"/>
+      <c r="BZ62"/>
+      <c r="CA62"/>
+      <c r="CB62"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A63" s="2"/>
+    <row r="63">
+      <c r="A63" s="4"/>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C63">
         <v>0.2</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E63">
         <v>0.24</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G63" s="10">
-        <v>0.79</v>
+        <v>120</v>
+      </c>
+      <c r="G63" s="42" t="n">
+        <v>79</v>
       </c>
       <c r="H63" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I63">
         <v>0.24</v>
       </c>
       <c r="J63" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="K63">
         <v>30</v>
       </c>
       <c r="L63" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M63">
         <v>0.2</v>
       </c>
       <c r="N63" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O63">
         <v>30</v>
@@ -4022,7 +7804,7 @@
         <v>30</v>
       </c>
       <c r="Q63" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R63">
         <v>4</v>
@@ -4030,11 +7812,72 @@
       <c r="S63">
         <v>3</v>
       </c>
+      <c r="T63"/>
+      <c r="U63"/>
+      <c r="V63"/>
+      <c r="W63"/>
+      <c r="X63"/>
+      <c r="Y63"/>
+      <c r="Z63"/>
+      <c r="AA63"/>
+      <c r="AB63"/>
+      <c r="AC63"/>
+      <c r="AD63"/>
+      <c r="AE63"/>
+      <c r="AF63"/>
+      <c r="AG63"/>
+      <c r="AH63"/>
+      <c r="AI63"/>
+      <c r="AJ63"/>
+      <c r="AK63"/>
+      <c r="AL63"/>
+      <c r="AM63"/>
+      <c r="AN63"/>
+      <c r="AO63"/>
+      <c r="AP63"/>
+      <c r="AQ63"/>
+      <c r="AR63"/>
+      <c r="AS63"/>
+      <c r="AT63"/>
+      <c r="AU63"/>
+      <c r="AV63"/>
+      <c r="AW63"/>
+      <c r="AX63"/>
+      <c r="AY63"/>
+      <c r="AZ63"/>
+      <c r="BA63"/>
+      <c r="BB63"/>
+      <c r="BC63"/>
+      <c r="BD63"/>
+      <c r="BE63"/>
+      <c r="BF63"/>
+      <c r="BG63"/>
+      <c r="BH63"/>
+      <c r="BI63"/>
+      <c r="BJ63"/>
+      <c r="BK63"/>
+      <c r="BL63"/>
+      <c r="BM63"/>
+      <c r="BN63"/>
+      <c r="BO63"/>
+      <c r="BP63"/>
+      <c r="BQ63"/>
+      <c r="BR63"/>
+      <c r="BS63"/>
+      <c r="BT63"/>
+      <c r="BU63"/>
+      <c r="BV63"/>
+      <c r="BW63"/>
+      <c r="BX63"/>
+      <c r="BY63"/>
+      <c r="BZ63"/>
+      <c r="CA63"/>
+      <c r="CB63"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I5" r:id="rId1" xr:uid="{8EECD2FE-C32C-43F4-8AF6-2679107A48E2}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{7B3F7082-5439-47DC-A411-7617647263D9}"/>
+    <hyperlink ref="I5" r:id="rIdCmccdbLink1"/>
+    <hyperlink ref="G5" r:id="rIdCmccdbLink2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
